--- a/deliverables/greenjobs_redesign_2026-09-22/tests_register_2026-09-28.xlsx
+++ b/deliverables/greenjobs_redesign_2026-09-22/tests_register_2026-09-28.xlsx
@@ -8,16 +8,18 @@
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Manual cases" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Automated Python" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Automated Node" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Not automatable" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Coverage" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Manual cases" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Automated Python" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Automated Node" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Not automatable" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Manual cases'!$A$1:$G$46</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Automated Python'!$A$1:$E$44</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Automated Node'!$A$1:$B$36</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Not automatable'!$A$1:$C$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Coverage'!$A$1:$D$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Manual cases'!$A$1:$G$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Automated Python'!$A$1:$E$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Automated Node'!$A$1:$B$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Not automatable'!$A$1:$C$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -446,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -487,7 +489,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>43 test functions, 319 checks, 0 failed</t>
+          <t>68 test functions across 3 files; 575 checks (test_build run incl. companions) + 126 gap checks + 87 scraper checks; 0 failed, 0 skipped</t>
         </is>
       </c>
     </row>
@@ -499,7 +501,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>35 tests, 35 pass, 0 failed</t>
+          <t>35 node tests pass; plus 15 Playwright checks on the live dashboard DOM</t>
         </is>
       </c>
     </row>
@@ -535,7 +537,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Manual cases · Automated Python · Automated Node · Not automatable</t>
+          <t>Coverage · Manual cases · Automated Python · Automated Node · Not automatable</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Python 78% → 99% (2026-09-28, second pass); see Coverage sheet</t>
         </is>
       </c>
     </row>
@@ -545,6 +559,285 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="110" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>File / check</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Before</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>After</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>build_site.py</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>88%</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>99%</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>5 lines: __main__ guard and resolve() guards that cannot raise on Python 3.11</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>validate_site.py</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>99%</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>2 lines: unreachable filesystem-root refusal</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>scrape_greenjobs.py</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>99%</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>1 line: __main__ guard; crawl replayed from 12 real pages recorded 2026-09-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL Python</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>78%</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>99%</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>8 of 2,101 statements uncovered</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>lib.js (node)</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>97.7%</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>97.7%</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>two edge branches</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>dashboard.js (node)</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>57.1% + 15 browser checks</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>DOM half runs in real Chromium (dashboard_dom.test.mjs); node cannot attribute browser-executed lines</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Mutation check: esc() quote=False</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr"/>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>caught</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>7 checks fail in test_gaps, 1 in test_build</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Mutation check: hero budget = 1 byte</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr"/>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>caught</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>8 checks fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Mutation check: landing 0-role guard removed</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr"/>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>caught</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>12 checks fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Mutation check: snapshot floor 0.5 → 0.1</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr"/>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>caught</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>test_scrape</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Mutation check: € mapped to GBP</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr"/>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>caught</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>test_scrape parse_salary</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Reproduce</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr"/>
+      <c r="C13" s="4" t="inlineStr"/>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>python3 -m coverage run --include="execution/gtm_client_workflows/greenjobs_redesign/*" tests/greenjobs_redesign/test_build.py &amp;&amp; python3 -m coverage report -m</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:D13"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2177,20 +2470,20 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E44"/>
+  <dimension ref="A1:E69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
     <col width="70" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2201,7 +2494,7 @@
       </c>
       <c r="B1" s="3" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>File</t>
         </is>
       </c>
       <c r="C1" s="3" t="inlineStr">
@@ -2211,12 +2504,12 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>Assertions</t>
+          <t>check() calls</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Line (test_build.py)</t>
+          <t>Line</t>
         </is>
       </c>
     </row>
@@ -2228,15 +2521,15 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>test_build.py</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr"/>
       <c r="D2" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3">
@@ -2247,15 +2540,15 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>test_build.py</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr"/>
       <c r="D3" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>51</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4">
@@ -2266,15 +2559,15 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>test_build.py</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr"/>
       <c r="D4" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>58</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5">
@@ -2285,15 +2578,15 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>test_build.py</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr"/>
       <c r="D5" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>68</v>
+        <v>77</v>
       </c>
     </row>
     <row r="6">
@@ -2304,15 +2597,15 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>test_build.py</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr"/>
       <c r="D6" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>80</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7">
@@ -2323,15 +2616,15 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>test_build.py</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr"/>
       <c r="D7" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>90</v>
+        <v>99</v>
       </c>
     </row>
     <row r="8">
@@ -2342,15 +2635,15 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>test_build.py</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr"/>
       <c r="D8" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>96</v>
+        <v>105</v>
       </c>
     </row>
     <row r="9">
@@ -2361,15 +2654,15 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>test_build.py</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr"/>
       <c r="D9" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>109</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10">
@@ -2380,15 +2673,15 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>test_build.py</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr"/>
       <c r="D10" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>114</v>
+        <v>123</v>
       </c>
     </row>
     <row r="11">
@@ -2399,15 +2692,15 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>test_build.py</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr"/>
       <c r="D11" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>126</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -2418,15 +2711,15 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>test_build.py</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr"/>
       <c r="D12" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>134</v>
+        <v>143</v>
       </c>
     </row>
     <row r="13">
@@ -2437,15 +2730,15 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>test_build.py</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr"/>
       <c r="D13" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>143</v>
+        <v>152</v>
       </c>
     </row>
     <row r="14">
@@ -2456,15 +2749,15 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>test_build.py</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr"/>
       <c r="D14" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>150</v>
+        <v>159</v>
       </c>
     </row>
     <row r="15">
@@ -2475,15 +2768,15 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>test_build.py</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr"/>
       <c r="D15" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>160</v>
+        <v>169</v>
       </c>
     </row>
     <row r="16">
@@ -2494,15 +2787,15 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>test_build.py</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr"/>
       <c r="D16" s="4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>170</v>
+        <v>179</v>
       </c>
     </row>
     <row r="17">
@@ -2513,15 +2806,15 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>test_build.py</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr"/>
       <c r="D17" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>192</v>
+        <v>201</v>
       </c>
     </row>
     <row r="18">
@@ -2532,15 +2825,15 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>test_build.py</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr"/>
       <c r="D18" s="4" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>210</v>
+        <v>219</v>
       </c>
     </row>
     <row r="19">
@@ -2551,15 +2844,15 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>dashboard / Keith round</t>
+          <t>test_build.py</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr"/>
       <c r="D19" s="4" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>272</v>
+        <v>281</v>
       </c>
     </row>
     <row r="20">
@@ -2570,15 +2863,15 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>dashboard / Keith round</t>
+          <t>test_build.py</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr"/>
       <c r="D20" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>308</v>
+        <v>317</v>
       </c>
     </row>
     <row r="21">
@@ -2589,15 +2882,15 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>dashboard / Keith round</t>
+          <t>test_build.py</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr"/>
       <c r="D21" s="4" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>323</v>
+        <v>332</v>
       </c>
     </row>
     <row r="22">
@@ -2608,15 +2901,15 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Keith round (B/D/G)</t>
+          <t>test_build.py</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr"/>
       <c r="D22" s="4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>371</v>
+        <v>380</v>
       </c>
     </row>
     <row r="23">
@@ -2627,15 +2920,15 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Keith round (B/D/G)</t>
+          <t>test_build.py</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr"/>
       <c r="D23" s="4" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>384</v>
+        <v>393</v>
       </c>
     </row>
     <row r="24">
@@ -2646,15 +2939,15 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Keith round (B/D/G)</t>
+          <t>test_build.py</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr"/>
       <c r="D24" s="4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>399</v>
+        <v>408</v>
       </c>
     </row>
     <row r="25">
@@ -2665,15 +2958,15 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Keith round (B/D/G)</t>
+          <t>test_build.py</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr"/>
       <c r="D25" s="4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>416</v>
+        <v>425</v>
       </c>
     </row>
     <row r="26">
@@ -2684,15 +2977,15 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Keith round (B/D/G)</t>
+          <t>test_build.py</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr"/>
       <c r="D26" s="4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>432</v>
+        <v>441</v>
       </c>
     </row>
     <row r="27">
@@ -2703,15 +2996,15 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Keith round (B/D/G)</t>
+          <t>test_build.py</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr"/>
       <c r="D27" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>458</v>
+        <v>467</v>
       </c>
     </row>
     <row r="28">
@@ -2722,15 +3015,15 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Keith round (B/D/G)</t>
+          <t>test_build.py</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr"/>
       <c r="D28" s="4" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>480</v>
+        <v>489</v>
       </c>
     </row>
     <row r="29">
@@ -2741,15 +3034,15 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>panel fixes A</t>
+          <t>test_build.py</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr"/>
       <c r="D29" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>513</v>
+        <v>522</v>
       </c>
     </row>
     <row r="30">
@@ -2760,15 +3053,15 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>panel fixes A</t>
+          <t>test_build.py</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr"/>
       <c r="D30" s="4" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>522</v>
+        <v>531</v>
       </c>
     </row>
     <row r="31">
@@ -2779,15 +3072,15 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>panel fixes A</t>
+          <t>test_build.py</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr"/>
       <c r="D31" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>547</v>
+        <v>556</v>
       </c>
     </row>
     <row r="32">
@@ -2798,15 +3091,15 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>panel fixes A</t>
+          <t>test_build.py</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr"/>
       <c r="D32" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>562</v>
+        <v>571</v>
       </c>
     </row>
     <row r="33">
@@ -2817,15 +3110,15 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>panel fixes A</t>
+          <t>test_build.py</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr"/>
       <c r="D33" s="4" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>595</v>
+        <v>604</v>
       </c>
     </row>
     <row r="34">
@@ -2836,15 +3129,15 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>panel fixes A</t>
+          <t>test_build.py</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr"/>
       <c r="D34" s="4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>622</v>
+        <v>631</v>
       </c>
     </row>
     <row r="35">
@@ -2855,15 +3148,15 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>panel fixes A</t>
+          <t>test_build.py</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr"/>
       <c r="D35" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>633</v>
+        <v>642</v>
       </c>
     </row>
     <row r="36">
@@ -2874,15 +3167,15 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>panel fixes A</t>
+          <t>test_build.py</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr"/>
       <c r="D36" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>644</v>
+        <v>653</v>
       </c>
     </row>
     <row r="37">
@@ -2893,15 +3186,15 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>panel fixes A</t>
+          <t>test_build.py</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr"/>
       <c r="D37" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>671</v>
+        <v>680</v>
       </c>
     </row>
     <row r="38">
@@ -2912,15 +3205,15 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>panel fixes A</t>
+          <t>test_build.py</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr"/>
       <c r="D38" s="4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>684</v>
+        <v>693</v>
       </c>
     </row>
     <row r="39">
@@ -2931,15 +3224,15 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>panel fixes A</t>
+          <t>test_build.py</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr"/>
       <c r="D39" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>705</v>
+        <v>714</v>
       </c>
     </row>
     <row r="40">
@@ -2950,15 +3243,15 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>panel fixes A</t>
+          <t>test_build.py</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr"/>
       <c r="D40" s="4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>720</v>
+        <v>729</v>
       </c>
     </row>
     <row r="41">
@@ -2969,15 +3262,15 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>panel fixes A</t>
+          <t>test_build.py</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr"/>
       <c r="D41" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>760</v>
+        <v>769</v>
       </c>
     </row>
     <row r="42">
@@ -2988,15 +3281,15 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>panel fixes A</t>
+          <t>test_build.py</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr"/>
       <c r="D42" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>771</v>
+        <v>780</v>
       </c>
     </row>
     <row r="43">
@@ -3007,15 +3300,15 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>panel fixes B</t>
+          <t>test_build.py</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr"/>
       <c r="D43" s="4" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>845</v>
+        <v>862</v>
       </c>
     </row>
     <row r="44">
@@ -3026,7 +3319,7 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>panel fixes B</t>
+          <t>test_build.py</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -3035,19 +3328,498 @@
         </is>
       </c>
       <c r="D44" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>936</v>
+        <v>953</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>test_parse_salary</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>test_scrape.py (recorded corpus)</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr"/>
+      <c r="D45" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="E45" s="4" t="n">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>test_text_helpers</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>test_scrape.py (recorded corpus)</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr"/>
+      <c r="D46" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="E46" s="4" t="n">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>test_parse_results_and_facets</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>test_scrape.py (recorded corpus)</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr"/>
+      <c r="D47" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="E47" s="4" t="n">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>test_parse_job_fields</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>test_scrape.py (recorded corpus)</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr"/>
+      <c r="D48" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="E48" s="4" t="n">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>test_measure_page</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>test_scrape.py (recorded corpus)</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr"/>
+      <c r="D49" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E49" s="4" t="n">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>test_fetch_error_branches</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>test_scrape.py (recorded corpus)</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr"/>
+      <c r="D50" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E50" s="4" t="n">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>test_snapshot_floor_and_atomic_write</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>test_scrape.py (recorded corpus)</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr"/>
+      <c r="D51" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="E51" s="4" t="n">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>test_crawl_ie</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>test_scrape.py (recorded corpus)</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr"/>
+      <c r="D52" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="E52" s="4" t="n">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>test_crawl_uk_with_logos_and_paging</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>test_scrape.py (recorded corpus)</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr"/>
+      <c r="D53" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="E53" s="4" t="n">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>test_crawl_paging_and_missing_page</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>test_scrape.py (recorded corpus)</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr"/>
+      <c r="D54" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E54" s="4" t="n">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>test_snapshot_floor_rejects_and_main_exit_code</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>test_scrape.py (recorded corpus)</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr"/>
+      <c r="D55" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E55" s="4" t="n">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>test_homepage_snapshot_fallback</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>test_scrape.py (recorded corpus)</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr"/>
+      <c r="D56" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E56" s="4" t="n">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>test_fixture_provenance</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>test_scrape.py (recorded corpus)</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr"/>
+      <c r="D57" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E57" s="4" t="n">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>test_helper_edges</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>test_gaps.py (branch tests)</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr"/>
+      <c r="D58" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="E58" s="4" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>test_dataset_and_brief</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>test_gaps.py (branch tests)</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr"/>
+      <c r="D59" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="E59" s="4" t="n">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>test_hero_footage_variants</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>test_gaps.py (branch tests)</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr"/>
+      <c r="D60" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="E60" s="4" t="n">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>test_geometry_helpers</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>test_gaps.py (branch tests)</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>svg_polygons / ring_area / point_in_rings / sample_map_points / film_payload</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E61" s="4" t="n">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>test_escaping_in_rendered_html</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>test_gaps.py (branch tests)</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr"/>
+      <c r="D62" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="E62" s="4" t="n">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>test_landing_zero_role_guard</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>test_gaps.py (branch tests)</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr"/>
+      <c r="D63" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="E63" s="4" t="n">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>test_node_and_js_checks</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>test_gaps.py (branch tests)</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr"/>
+      <c r="D64" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="E64" s="4" t="n">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>test_guard_output_edges</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>test_gaps.py (branch tests)</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr"/>
+      <c r="D65" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E65" s="4" t="n">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>test_build_failure_exits</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>test_gaps.py (branch tests)</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr"/>
+      <c r="D66" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E66" s="4" t="n">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>test_rebuild_and_no_site_base</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>test_gaps.py (branch tests)</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr"/>
+      <c r="D67" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E67" s="4" t="n">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>test_cli_main_with_today</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>test_gaps.py (branch tests)</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr"/>
+      <c r="D68" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E68" s="4" t="n">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>test_validator_every_message</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>test_gaps.py (branch tests)</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr"/>
+      <c r="D69" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E69" s="4" t="n">
+        <v>383</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E44"/>
+  <autoFilter ref="A1:E69"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3498,7 +4270,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/deliverables/greenjobs_redesign_2026-09-22/tests_register_2026-09-28.xlsx
+++ b/deliverables/greenjobs_redesign_2026-09-22/tests_register_2026-09-28.xlsx
@@ -8,18 +8,20 @@
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Coverage" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Manual cases" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Automated Python" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Automated Node" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Not automatable" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Keith requirements" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Coverage" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Manual cases" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Automated Python" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Automated Node" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Not automatable" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Coverage'!$A$1:$D$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Manual cases'!$A$1:$G$46</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Automated Python'!$A$1:$E$69</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Automated Node'!$A$1:$B$36</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Not automatable'!$A$1:$C$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Keith requirements'!$A$1:$H$115</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Coverage'!$A$1:$D$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Manual cases'!$A$1:$G$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Automated Python'!$A$1:$E$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Automated Node'!$A$1:$B$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Not automatable'!$A$1:$C$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -48,7 +50,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -58,6 +60,31 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="002F5D3A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E3F1E3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDE9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3CD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2E3F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8D7DA"/>
       </patternFill>
     </fill>
   </fills>
@@ -73,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -81,6 +108,21 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -448,7 +490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -553,12 +595,4135 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Keith's document, sentence by sentence (114 rows, re-verified on the final build)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>DONE: 96, INTERPRETED DIFFERENTLY: 3, PARTIAL: 7, NEEDS CLIENT INPUT: 7, NOT DONE: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Visual sweep (32 issues found by a picky pass + 6 found on re-check)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>All fixable ones fixed and re-screenshotted; see research/qa_2026-09-28/visual_issues_v2.md</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H115"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="70" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>section</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>requirement_verbatim</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>edition</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>delta</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>changed_since_v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>R001</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Proposition</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>“Work that puts the planet on the payroll” is memorable, but slightly abstract. I prefer: Work that works for the planet or Build your career. Protect our future.</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>IE+UK</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>/ie/ and /uk/ hero h1 text = "Work that works for the planet." (grep ie/index.html, uk/index.html; shots ie_home_1440_light, uk_home_1440_dark)</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr"/>
+      <c r="H2" s="5" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>R002</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Proposition</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Find environmental, sustainability, renewable-energy and nature careers across Ireland.</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>/ie/ hero subheading is the exact sentence (ie/index.html text dump)</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr"/>
+      <c r="H3" s="5" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>R003</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Remove “3 employers”</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Remove “3 employers” from the hero</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>/ie/ hero strip = "88 live roles · Specialist green job network since 2008 · 10 specialist job sites · Roles across 14 sectors · Snapshot of 22 September 2026"; no employer count in the strip</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>Count still appears lower on /ie/ and /ie/employers/: "3 of them have live roles on greenjobs.ie this week" (grep "3 of them")</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>R004</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Remove “3 employers”</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Specialist green job network since 2008</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>IE+UK</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>Both hero strips contain "Specialist green job network since 2008"</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr"/>
+      <c r="H5" s="5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>R005</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Remove “3 employers”</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>10 specialist job sites</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>IE+UK</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>Both hero strips contain "10 specialist job sites"</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr"/>
+      <c r="H6" s="5" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>R006</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Remove “3 employers”</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Roles across 10 sectors</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>IE+UK</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>INTERPRETED DIFFERENTLY</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>Hero strip now reads "Roles across 14 sectors" on both editions (was 15/14); computed from sectors with &gt;=1 live role</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Client wrote 10; site shows the live count 14. Still needs the client to confirm which number</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>R007</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Remove “3 employers”</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Certified B Corporation</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>IE+UK</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>Header badge now has a text label "Certified B Corp" (span.hdr__bcorp) + hero pill "Certified B Corporation. Independently verified for…" on both editions (crop ie_home_hero)</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>Label added since v1</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>R008</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Road engineering and infrastructure roles appear under “Sustainability &amp; net zero.”</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>IE+UK</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>"Sustainability &amp; net zero" appears in no page except the for-keith evidence quote; Assistant Road Engineer / Highways Civil Engineer tagged "Sustainable infrastructure &amp; transport" only (jobs.json)</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr"/>
+      <c r="H9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>R009</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>UK-only roles also appear prominently on the Irish board with salaries converted into euros.</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>INTERPRETED DIFFERENTLY</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>Per Keith's 28-Sept rule (KEITH_CHANGES_CHECKLIST B5) the IE board keeps UK-only roles, labelled "UK", with the toggle doing the excluding. jobs.json IE: 62 ie / 23 uk / 3 cross; 21 of the 23 UK roles now show advertised sterling "£62k–67k (paid in sterling, about €72.5k–78.4k)" (/ie/ first card, /ie/jobs/11501460/)</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>Was NOT DONE. Prominence is now a client decision; 2 UK-only roles (11497629 Associate Civil Engineer London €70–75k, 11496364 Planner Scotland €30–40k) still carry euro figures with no "Salary source" row</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>NOT DONE → INTERPRETED DIFFERENTLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>R010</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>Improve sector mapping.</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>IE+UK</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>14-sector taxonomy; Highways Civil Engineer (uk 11501402) and Assistant Road Engineer now single-tagged infrastructure; Design Coordinator – Rail, Principal Engineer – Transportation, Civil Engineering Technician all "Sustainable infrastructure &amp; transport"</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>Associate Civil Engineer (ie 11497629) still also tagged "Built environment &amp; energy efficiency"; Principal Project Manager – Civil &amp; Environmental sits under Environmental engineering + Waste</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>R011</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>Retain salaries in their original advertised currency.</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>IE+UK</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>UK: /uk/jobs/11501639/ "€5.1k–6k/mo (paid in euros, about £4.4k–5.1k/mo)". IE: /ie/jobs/11500760/ Salary "£45,000 to £55,000 per annum (paid in sterling, about €52.7k–64.3k)" + "Salary source: Advertised in sterling on the greenjobs.co.uk listing"; IE jobs.json cur: 21 GBP, 8 EUR, 59 none</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>Improved: 21/23 IE sterling roles restored. 2 UK-located roles (11497629, 11496364) still show € figures; scraped from greenjobs.ie with no UK twin, so the original currency is unverified</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>R012</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Clearly label UK, Ireland, remote and cross-border positions.</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>IE+UK</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>Chips "UK", "Ireland", "Ireland &amp; UK", "Remote"; Commonland roles now "Dublin · Ireland &amp; UK" on /ie/ and /ie/jobs/ (was "Dublin · Ireland"); /ie/jobs/11500760/ facts panel "Where: UK"</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>Cross-border labelling fixed since v1</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>PARTIAL → DONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>R013</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Allow users to exclude UK opportunities.</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>/ie/jobs/ checkbox "Hide UK/abroad-only roles — Keeps Ireland, Northern Ireland, remote and Ireland-and-UK roles; hides roles advertised only in the UK or abroad."</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr"/>
+      <c r="H14" s="5" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>R014</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Explain when one job appears in multiple counties or sectors, as totals otherwise look inconsistent.</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>IE+UK</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>/ie/ "A role listed in more than one county or sector counts in each; salary figures use the midpoint…"; /ie/jobs/, /ie/sectors/, salary guide carry the same note</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr"/>
+      <c r="H15" s="5" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>R015</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Shorten the homepage</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>County information appears twice.</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>/ie/ has one county mention: stat tile "14 counties with live roles"; no county map on home</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr"/>
+      <c r="H16" s="5" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>R016</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Shorten the homepage</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Sector information appears twice.</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>IE+UK</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>One "Browse by sector" section per home page (9 cards + "All sectors")</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr"/>
+      <c r="H17" s="5" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>R017</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Shorten the homepage</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Salary transparency appears in several places.</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>IE+UK</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>One "Salary insight" section per home; sector cards carry only a median/disclosure line</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr"/>
+      <c r="H18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>R018</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Shorten the homepage</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>The CV-matching tool is repeated on the jobs page.</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>IE+UK</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>"Quick job match" only on /ie/jobs/ and /uk/jobs/ (grep home pages: 0)</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr"/>
+      <c r="H19" s="5" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>R019</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Shorten the homepage</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>A simpler sequence would be: Hero and search</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>/ie/ order: hero+search → Latest roles → Browse by sector → Salary insight → Why GreenJobs → Employer proposition → Email alerts (text dump)</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr"/>
+      <c r="H20" s="5" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>R020</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Shorten the homepage</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Featured/latest roles</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>/ie/ "Latest roles" (8 cards) second</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr"/>
+      <c r="H21" s="5" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>R021</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Shorten the homepage</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Browse by sector</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>/ie/ "Browse by sector" third</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr"/>
+      <c r="H22" s="5" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>R022</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Shorten the homepage</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Salary insight</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>/ie/ "Salary insight" fourth</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr"/>
+      <c r="H23" s="5" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>R023</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Shorten the homepage</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Why GreenJobs</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>/ie/ "Why GreenJobs" fifth</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr"/>
+      <c r="H24" s="5" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>R024</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Shorten the homepage</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Employer proposition</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>/ie/ "Employer proposition" sixth</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr"/>
+      <c r="H25" s="5" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>R025</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Shorten the homepage</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Email alerts</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>/ie/ "Email alerts: the week's green roles, in your inbox" last</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr"/>
+      <c r="H26" s="5" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>R026</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Shorten the homepage</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>The interactive data elements are good, but there are currently too many competing for attention.</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>IE+UK</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>IE home: sector sparklines + 3 stat tiles; UK home: one region map + 3 stat tiles (shots ie_home_1440_light, uk_home_1440_dark)</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr"/>
+      <c r="H27" s="5" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>R027</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Candidate experience</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Workplace type: office, hybrid, remote or site-based</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>IE+UK</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>/uk/jobs/ Workplace: Office-based, Hybrid, Remote, Site-based, Not stated; /ie/jobs/ omits Office-based (jobs.json IE has 0 office roles)</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr"/>
+      <c r="H28" s="5" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>R028</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Candidate experience</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Career level</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>IE+UK</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>Career level select: Graduate/Early career, Mid-level, Senior/Principal, Director/Associate (both editions)</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr"/>
+      <c r="H29" s="5" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>R029</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Candidate experience</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Salary range</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>IE+UK</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>"Salary, EUR/GBP a year" Minimum/Maximum + "Salary disclosed only" + note "Ranges are compared per year in EUR; every role still shows the salary in the currency it was advertised in."</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr"/>
+      <c r="H30" s="5" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>R030</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Candidate experience</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Permanent, contract, fixed-term, full-time and part-time</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>IE+UK</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>Single "Contract" select: Permanent, Contract, Fixed-term, Full-time (+Part-time, Volunteer on UK). The overlapping "Job type" select is gone (grep "Job type": 0)</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>Duplicate select removed since v1</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>R031</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>Candidate experience</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>Ireland-only toggle</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>/ie/jobs/ "Hide UK/abroad-only roles" checkbox</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr"/>
+      <c r="H32" s="5" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>R032</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Candidate experience</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>Closing date</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>IE+UK</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>Closing date select: Any / within 7 / 14 / 30 days + "Hide closed roles"</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr"/>
+      <c r="H33" s="5" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>R033</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>Candidate experience</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>Direct employer versus recruitment agency</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>IE+UK</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>"Advertised by": Employers and agencies / Direct employer / Recruitment agency; job pages show "Advertised by: Recruitment agency"</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr"/>
+      <c r="H34" s="5" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>R034</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Candidate experience</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>“Similar jobs” on individual vacancy pages</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>IE+UK</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>/ie/jobs/11500760/, /ie/jobs/11501460/, /uk/jobs/11501639/, /uk/jobs/11501402/ each have "Similar roles — Same sector first, then the same area, then similar pay" with 4 cards</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr"/>
+      <c r="H35" s="5" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>R035</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>Candidate experience</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>Rename “Your fit in ten seconds” to something more credible, such as Quick job match.</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>IE+UK</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>h2 "Quick job match" on both jobs pages; "Your fit in ten seconds" only in the for-keith quote</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr"/>
+      <c r="H36" s="5" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>R036</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Candidate experience</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>Put this directly beside the input: Your information is processed on your device and is not uploaded or stored.</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>IE+UK</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>Both jobs pages: "Your information is processed on your device and is not uploaded or stored." rendered in bold beside (right of) the textarea at 1440 (crop ie_jobsmap_top)</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>Exact sentence and placement fixed since v1</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>PARTIAL → DONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>R037</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>Candidate experience</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>Also make clear that it is keyword matching, not a formal assessment of someone’s suitability.</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>IE+UK</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>Directly under it: "Keyword matching, not an assessment of your suitability."</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr"/>
+      <c r="H38" s="5" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>R038</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Employer conversion</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>Actual prices or a clear “Request advertising rates” CTA</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>IE+UK</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>/ie/employers/ and /uk/employers/: "Request advertising rates →" in hero, above the table and in the form; "Prices are not published. Rates are supplied by the team…"</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr"/>
+      <c r="H39" s="5" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="8" t="inlineStr">
+        <is>
+          <t>R039</t>
+        </is>
+      </c>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>Employer conversion</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t>Candidate audience and newsletter reach</t>
+        </is>
+      </c>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>IE+UK</t>
+        </is>
+      </c>
+      <c r="E40" s="8" t="inlineStr">
+        <is>
+          <t>NEEDS CLIENT INPUT</t>
+        </is>
+      </c>
+      <c r="F40" s="8" t="inlineStr">
+        <is>
+          <t>"Audience and reach" block reads "Thousands of visitors every month…" then "Monthly visitor figures are published at launch." / "Subscriber numbers are published at launch."</t>
+        </is>
+      </c>
+      <c r="G40" s="8" t="inlineStr">
+        <is>
+          <t>Placeholder wording softened but figures still missing; client must supply</t>
+        </is>
+      </c>
+      <c r="H40" s="8" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>R040</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>Employer conversion</t>
+        </is>
+      </c>
+      <c r="C41" s="8" t="inlineStr">
+        <is>
+          <t>LinkedIn and network distribution figures</t>
+        </is>
+      </c>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>IE+UK</t>
+        </is>
+      </c>
+      <c r="E41" s="8" t="inlineStr">
+        <is>
+          <t>NEEDS CLIENT INPUT</t>
+        </is>
+      </c>
+      <c r="F41" s="8" t="inlineStr">
+        <is>
+          <t>"Network and LinkedIn distribution" ends "Network and follower numbers are published at launch."</t>
+        </is>
+      </c>
+      <c r="G41" s="8" t="inlineStr">
+        <is>
+          <t>Client must supply</t>
+        </is>
+      </c>
+      <c r="H41" s="8" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>R041</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>Employer conversion</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>Examples of organisations that have recruited through GreenJobs</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>IE+UK</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>UK: 12 logo tiles in the marquee (Arup, Commonland, Dacorum, ESS, Gaia, Grundon, Haskoning, Jacobs…). IE: Mattinson logo + text-only tiles "Commonland", "Gaia Talent" (crop ie_home_employers); EirGrid/Power NI/Veolia dropped</t>
+        </is>
+      </c>
+      <c r="G42" s="7" t="inlineStr">
+        <is>
+          <t>IE tiles still text-only; only organisations with live roles are shown now</t>
+        </is>
+      </c>
+      <c r="H42" s="7" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>R042</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>Employer conversion</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>A comparison table for Standard, Premium and Membership packages</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>IE+UK</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>"Compare the options" table renders as a proper 4-column grid with green "Included" ticks and muted "Ask us" (crop ie_emp_table); at 390 it collapses to one card per row (crop ie_emp390_table)</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>Rendering fixed since v1. New defect: .cmpwrap max-height 648px hides the last two rows (the Membership "Included" rows) at 1440×900 with no scroll cue — see visual_issues_v2 N1</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>PARTIAL → DONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>R043</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>Employer conversion</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="inlineStr">
+        <is>
+          <t>“Employer branding” and “Packages and memberships” currently feel like headings rather than fully developed products.</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>IE+UK</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="F44" s="7" t="inlineStr">
+        <is>
+          <t>Headings replaced by "Audience and reach", "Compare the options", "Post a job"; Membership column is 11×"Ask us" + 2 Included</t>
+        </is>
+      </c>
+      <c r="G44" s="7" t="inlineStr">
+        <is>
+          <t>Products remain thin; needs client content</t>
+        </is>
+      </c>
+      <c r="H44" s="7" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>R044</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>Employer conversion</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>The live site should concentrate on the outcome: Preview exactly how your vacancy will appear to candidates.</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>IE+UK</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>Lede "Preview exactly how your vacancy will appear to candidates."; remaining form note is "Preview only. Rates and posting are handled by the GreenJobs team." (no "Posting opens at launch", grep 0)</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>Launch disclaimer removed since v1</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>PARTIAL → DONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>R045</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>Copy and credibility</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>“Career level read from title”</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>IE+UK</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>grep across site HTML: only in for-keith evidence quote (noindex)</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="inlineStr"/>
+      <c r="H46" s="5" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>R046</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>Copy and credibility</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>“Tagged by what its description actually says”</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>IE+UK</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>grep: only in for-keith quote; dashboard says "each role is tagged to the sectors its description talks about"</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr"/>
+      <c r="H47" s="5" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>R047</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>Copy and credibility</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>“The send button is honest”</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>IE+UK</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F48" s="5" t="inlineStr">
+        <is>
+          <t>grep: only in for-keith quote</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="inlineStr"/>
+      <c r="H48" s="5" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>R048</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>Copy and credibility</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>Replace this with benefit-led language: Every vacancy is classified consistently, making it easier to compare roles, sectors and salaries.</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>IE+UK</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>Exact sentence on /ie/, /uk/ "Browse by sector" and /ie/sectors/, /uk/sectors/</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="inlineStr"/>
+      <c r="H49" s="5" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>R049</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>Copy and credibility</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>Instead of repeatedly stating that employers say “competitive,” position: Compare disclosed salaries and identify employers committed to greater pay transparency.</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>IE+UK</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t>Exact sentence on home "Salary insight", /ie/insights/, /uk/insights/ and both salary guides</t>
+        </is>
+      </c>
+      <c r="G50" s="5" t="inlineStr"/>
+      <c r="H50" s="5" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>R050</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>Additional improvements</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>Give the B Corp badge a short explanation</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>IE+UK</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>Hero pill (2 lines at 1440, crop ie_home_hero) + footer line + header title attribute</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="inlineStr">
+        <is>
+          <t>Wrap fixed since v1</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>R051</t>
+        </is>
+      </c>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>Additional improvements</t>
+        </is>
+      </c>
+      <c r="C52" s="7" t="inlineStr">
+        <is>
+          <t>Add salary guides, market reports and career advice to build repeat traffic</t>
+        </is>
+      </c>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>IE+UK</t>
+        </is>
+      </c>
+      <c r="E52" s="7" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="F52" s="7" t="inlineStr">
+        <is>
+          <t>/ie/guides/: "Green salary guide for Ireland" + 4 job-market pages; empty "Career advice and market reports" heading removed, replaced by "More guides follow as the data grows."</t>
+        </is>
+      </c>
+      <c r="G52" s="7" t="inlineStr">
+        <is>
+          <t>No career-advice or market-report content yet</t>
+        </is>
+      </c>
+      <c r="H52" s="7" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>R052</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>Additional improvements</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>Create dedicated SEO landing pages such as “Ecology Jobs Ireland,” “Environmental Jobs Dublin” and “Renewable Energy Jobs Ireland.”</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>IE+UK</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <t>/ie/ecology-jobs-ireland/, /ie/environmental-jobs-dublin/, /ie/renewable-energy-jobs-ireland/, /ie/sustainability-jobs-ireland/ + UK equivalents all 200</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="inlineStr">
+        <is>
+          <t>IE ecology page lists 2 London Mattinson roles labelled "UK" (kept per Keith rule)</t>
+        </is>
+      </c>
+      <c r="H53" s="5" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>R053</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>Additional improvements</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>Implement JobPosting structured data</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>IE+UK</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F54" s="5" t="inlineStr">
+        <is>
+          <t>&lt;script type="application/ld+json"&gt; JobPosting with Organization, Place, PostalAddress, MonetaryAmount(currency GBP on IE 11500760, EUR on UK 11501639)</t>
+        </is>
+      </c>
+      <c r="G54" s="5" t="inlineStr"/>
+      <c r="H54" s="5" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>R054</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>Additional improvements</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>canonical URLs</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>IE+UK</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>&lt;link rel="canonical"&gt; on every fetched page</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="inlineStr">
+        <is>
+          <t>Still points at greenjobs-redesign.pages.dev/…/index.html and every page is noindex,nofollow (demo)</t>
+        </is>
+      </c>
+      <c r="H55" s="5" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>R055</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>Additional improvements</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>IE/UK hreflang</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>IE+UK</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F56" s="5" t="inlineStr">
+        <is>
+          <t>hreflang en-IE / en-GB / x-default now on landing pages (/ie/ecology-jobs-ireland/ ↔ /uk/ecology-jobs-uk/), guides, salary guide, dashboard; job pages carry canonical only (no twin)</t>
+        </is>
+      </c>
+      <c r="G56" s="5" t="inlineStr">
+        <is>
+          <t>Landing/guide pairs added since v1</t>
+        </is>
+      </c>
+      <c r="H56" s="5" t="inlineStr">
+        <is>
+          <t>PARTIAL → DONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>R056</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>Additional improvements</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>Test the map, animations and interactive tools for keyboard access</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>IE+UK</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>Playwright: UK map regions role=button tabindex=0 aria-label ("East Midlands: 0 roles", "Northern Ireland: 0 roles"); 404 and dialogs keyboard-closable (data-sheet-close, dialog close)</t>
+        </is>
+      </c>
+      <c r="G57" s="5" t="inlineStr"/>
+      <c r="H57" s="5" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>R057</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>Additional improvements</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>reduced-motion preferences</t>
+        </is>
+      </c>
+      <c r="D58" s="5" t="inlineStr">
+        <is>
+          <t>IE+UK</t>
+        </is>
+      </c>
+      <c r="E58" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F58" s="5" t="inlineStr">
+        <is>
+          <t>css/styles.css has 4 prefers-reduced-motion blocks; marquee pauses on hover/focus-within (.marq:focus-within … animation-play-state:paused)</t>
+        </is>
+      </c>
+      <c r="G58" s="5" t="inlineStr"/>
+      <c r="H58" s="5" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t>R058</t>
+        </is>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>Additional improvements</t>
+        </is>
+      </c>
+      <c r="C59" s="7" t="inlineStr">
+        <is>
+          <t>mobile performance</t>
+        </is>
+      </c>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>IE+UK</t>
+        </is>
+      </c>
+      <c r="E59" s="7" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="F59" s="7" t="inlineStr">
+        <is>
+          <t>/ie/jobs/index.html 300 KB, /uk/jobs/index.html 271 KB (inline JSON); ie/data/jobs.json duplicated at 219 KB; no Lighthouse/field data</t>
+        </is>
+      </c>
+      <c r="G59" s="7" t="inlineStr">
+        <is>
+          <t>Unchanged since v1</t>
+        </is>
+      </c>
+      <c r="H59" s="7" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="8" t="inlineStr">
+        <is>
+          <t>R059</t>
+        </is>
+      </c>
+      <c r="B60" s="8" t="inlineStr">
+        <is>
+          <t>Additional improvements</t>
+        </is>
+      </c>
+      <c r="C60" s="8" t="inlineStr">
+        <is>
+          <t>Replace “3 employers” with employer logos only if each relationship and permission to display the logo are current.</t>
+        </is>
+      </c>
+      <c r="D60" s="8" t="inlineStr">
+        <is>
+          <t>IE+UK</t>
+        </is>
+      </c>
+      <c r="E60" s="8" t="inlineStr">
+        <is>
+          <t>NEEDS CLIENT INPUT</t>
+        </is>
+      </c>
+      <c r="F60" s="8" t="inlineStr">
+        <is>
+          <t>IE strip shows only the 3 organisations with live roles (Mattinson logo, Commonland/Gaia text); UK strip 12 logos from listings</t>
+        </is>
+      </c>
+      <c r="G60" s="8" t="inlineStr">
+        <is>
+          <t>Text tiles for Commonland/Gaia; permissions still to be confirmed by client</t>
+        </is>
+      </c>
+      <c r="H60" s="8" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>R060</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>UK: geography</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>The UK homepage currently contains too much Irish inventory / tighter geographic separation</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F61" s="5" t="inlineStr">
+        <is>
+          <t>uk/data/jobs.json: 77 = 74 uk + 3 cross; 0 ie-only</t>
+        </is>
+      </c>
+      <c r="G61" s="5" t="inlineStr"/>
+      <c r="H61" s="5" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>R061</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>UK: geography</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>Keep Irish-only vacancies off the UK homepage — Two Dublin-only Gaia roles appear in the latest UK vacancies.</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E62" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F62" s="5" t="inlineStr">
+        <is>
+          <t>/uk/ Latest UK roles: 8 cards, none Dublin-only; Gaia role shown as "Dublin, United Kingdom (UK) · Ireland &amp; UK"</t>
+        </is>
+      </c>
+      <c r="G62" s="5" t="inlineStr"/>
+      <c r="H62" s="5" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>R062</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>UK: geography</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>23 of the 98 roles are classified as “Ireland &amp; abroad.”</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F63" s="5" t="inlineStr">
+        <is>
+          <t>No "Ireland &amp; abroad" bucket (grep 0); headline 77; "13 roles are not on the map: UK-wide / remote (13)"</t>
+        </is>
+      </c>
+      <c r="G63" s="5" t="inlineStr"/>
+      <c r="H63" s="5" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>R063</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>UK: geography</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>Only show a vacancy on the UK edition where it is: Located in the UK</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E64" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F64" s="5" t="inlineStr">
+        <is>
+          <t>uk jobs.json loc_class: 74 uk</t>
+        </is>
+      </c>
+      <c r="G64" s="5" t="inlineStr"/>
+      <c r="H64" s="5" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>R064</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>UK: geography</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>Fully remote and open to UK residents</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E65" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F65" s="5" t="inlineStr">
+        <is>
+          <t>7 remote-workplace roles in UK dataset; Workplace filter has Remote</t>
+        </is>
+      </c>
+      <c r="G65" s="5" t="inlineStr"/>
+      <c r="H65" s="5" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>R065</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>UK: geography</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>Explicitly available in both the UK and Ireland</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E66" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F66" s="5" t="inlineStr">
+        <is>
+          <t>3 "cross" roles labelled "Ireland &amp; UK"</t>
+        </is>
+      </c>
+      <c r="G66" s="5" t="inlineStr"/>
+      <c r="H66" s="5" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>R066</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>UK: geography</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>The headline should reflect genuine UK availability, not the entire shared database.</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F67" s="5" t="inlineStr">
+        <is>
+          <t>/uk/ "77 live green roles across the UK this week"</t>
+        </is>
+      </c>
+      <c r="G67" s="5" t="inlineStr"/>
+      <c r="H67" s="5" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>R067</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>UK: geography</t>
+        </is>
+      </c>
+      <c r="C68" s="5" t="inlineStr">
+        <is>
+          <t>Do not show euro salaries without explanation — The Commonland role displays €5.1k–€6k/month on the UK homepage.</t>
+        </is>
+      </c>
+      <c r="D68" s="5" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E68" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F68" s="5" t="inlineStr">
+        <is>
+          <t>/uk/ card: "€5.1k–6k/mo" chip + separate "paid in € ≈ £4.4k–5.1k/mo" chip (crop uk_home_marquee_after3s)</t>
+        </is>
+      </c>
+      <c r="G68" s="5" t="inlineStr">
+        <is>
+          <t>Long chip split in two since v1; no mid-value wrap at 390 (crop uk_home390_mid)</t>
+        </is>
+      </c>
+      <c r="H68" s="5" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>R068</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>UK: geography</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>Show the original salary with a clear “salary paid in euros” label</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E69" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F69" s="5" t="inlineStr">
+        <is>
+          <t>"(paid in euros, about £4.4k–5.1k/mo)" on the job page; "paid in €" chip on cards</t>
+        </is>
+      </c>
+      <c r="G69" s="5" t="inlineStr"/>
+      <c r="H69" s="5" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>R069</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="inlineStr">
+        <is>
+          <t>UK: geography</t>
+        </is>
+      </c>
+      <c r="C70" s="5" t="inlineStr">
+        <is>
+          <t>Provide an approximate sterling equivalent alongside it.</t>
+        </is>
+      </c>
+      <c r="D70" s="5" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E70" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F70" s="5" t="inlineStr">
+        <is>
+          <t>"about £4.4k–5.1k/mo"</t>
+        </is>
+      </c>
+      <c r="G70" s="5" t="inlineStr"/>
+      <c r="H70" s="5" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>R070</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>UK: geography</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>Do not silently convert salaries for UK vacancies.</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F71" s="5" t="inlineStr">
+        <is>
+          <t>UK dataset: 46 GBP, 1 EUR (labelled), 30 undisclosed</t>
+        </is>
+      </c>
+      <c r="G71" s="5" t="inlineStr"/>
+      <c r="H71" s="5" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>R071</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>UK: geography</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>“Every region, counted” is slightly misleading</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E72" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F72" s="5" t="inlineStr">
+        <is>
+          <t>"Every region, counted" only in for-keith quote; section h2 "See where green employers are hiring"</t>
+        </is>
+      </c>
+      <c r="G72" s="5" t="inlineStr"/>
+      <c r="H72" s="5" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="7" t="inlineStr">
+        <is>
+          <t>R072</t>
+        </is>
+      </c>
+      <c r="B73" s="7" t="inlineStr">
+        <is>
+          <t>UK: geography</t>
+        </is>
+      </c>
+      <c r="C73" s="7" t="inlineStr">
+        <is>
+          <t>Northern Ireland is absent.</t>
+        </is>
+      </c>
+      <c r="D73" s="7" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E73" s="7" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="F73" s="7" t="inlineStr">
+        <is>
+          <t>Map has a Northern Ireland region (aria "Northern Ireland: 0 roles"); region list now includes "Northern Ireland 0" and the datalist has an "Northern Ireland" option (uk/jobs/index.html)</t>
+        </is>
+      </c>
+      <c r="G73" s="7" t="inlineStr">
+        <is>
+          <t>Improved: NI is a filter option now. NI still renders as a dark hole on the map (crop uk_home_map) — see visual #12</t>
+        </is>
+      </c>
+      <c r="H73" s="7" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>R073</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t>UK: geography</t>
+        </is>
+      </c>
+      <c r="C74" s="5" t="inlineStr">
+        <is>
+          <t>East Midlands is absent.</t>
+        </is>
+      </c>
+      <c r="D74" s="5" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E74" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F74" s="5" t="inlineStr">
+        <is>
+          <t>Region list shows "East Midlands 0"; map region aria "East Midlands: 0 roles"</t>
+        </is>
+      </c>
+      <c r="G74" s="5" t="inlineStr">
+        <is>
+          <t>Listed at 0 since v1</t>
+        </is>
+      </c>
+      <c r="H74" s="5" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>R074</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>UK: geography</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="inlineStr">
+        <is>
+          <t>Ireland and overseas roles are grouped separately.</t>
+        </is>
+      </c>
+      <c r="D75" s="5" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E75" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F75" s="5" t="inlineStr">
+        <is>
+          <t>Only "UK-wide / remote (13)" as the off-map group</t>
+        </is>
+      </c>
+      <c r="G75" s="5" t="inlineStr"/>
+      <c r="H75" s="5" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>R075</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="inlineStr">
+        <is>
+          <t>UK: geography</t>
+        </is>
+      </c>
+      <c r="C76" s="5" t="inlineStr">
+        <is>
+          <t>UK-wide roles are not shown on the map.</t>
+        </is>
+      </c>
+      <c r="D76" s="5" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E76" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F76" s="5" t="inlineStr">
+        <is>
+          <t>"13 roles are not on the map: UK-wide / remote (13)" link beside the map</t>
+        </is>
+      </c>
+      <c r="G76" s="5" t="inlineStr"/>
+      <c r="H76" s="5" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>R076</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>UK: geography</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>A better heading would be: See where green employers are hiring — Explore current vacancies by UK region, including nationwide and remote opportunities.</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E77" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F77" s="5" t="inlineStr">
+        <is>
+          <t>/uk/ h2 + lede are the exact sentences</t>
+        </is>
+      </c>
+      <c r="G77" s="5" t="inlineStr"/>
+      <c r="H77" s="5" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t>R077</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="inlineStr">
+        <is>
+          <t>UK: geography</t>
+        </is>
+      </c>
+      <c r="C78" s="5" t="inlineStr">
+        <is>
+          <t>Northern Ireland should be included as a clear location option</t>
+        </is>
+      </c>
+      <c r="D78" s="5" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E78" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F78" s="5" t="inlineStr">
+        <is>
+          <t>"Northern Ireland" appears in the region list (0) and in the /uk/jobs/ region datalist (grep count 5)</t>
+        </is>
+      </c>
+      <c r="G78" s="5" t="inlineStr">
+        <is>
+          <t>Was PARTIAL; option added since v1</t>
+        </is>
+      </c>
+      <c r="H78" s="5" t="inlineStr">
+        <is>
+          <t>PARTIAL → DONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>R078</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="inlineStr">
+        <is>
+          <t>UK: matching examples</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t>Remove Dublin from the matching example (ecologist dublin)</t>
+        </is>
+      </c>
+      <c r="D79" s="5" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E79" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F79" s="5" t="inlineStr">
+        <is>
+          <t>/uk/jobs/ examples: no Dublin; placeholder ends "…EIA chapters, Bristol"</t>
+        </is>
+      </c>
+      <c r="G79" s="5" t="inlineStr"/>
+      <c r="H79" s="5" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>R079</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="inlineStr">
+        <is>
+          <t>UK: matching examples</t>
+        </is>
+      </c>
+      <c r="C80" s="5" t="inlineStr">
+        <is>
+          <t>ecologist Bristol</t>
+        </is>
+      </c>
+      <c r="D80" s="5" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E80" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F80" s="5" t="inlineStr">
+        <is>
+          <t>"Try:" chip "ecologist Bristol"</t>
+        </is>
+      </c>
+      <c r="G80" s="5" t="inlineStr"/>
+      <c r="H80" s="5" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>R080</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>UK: matching examples</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>sustainability consultant London</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E81" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F81" s="5" t="inlineStr">
+        <is>
+          <t>chip "sustainability consultant London"</t>
+        </is>
+      </c>
+      <c r="G81" s="5" t="inlineStr"/>
+      <c r="H81" s="5" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>R081</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="inlineStr">
+        <is>
+          <t>UK: matching examples</t>
+        </is>
+      </c>
+      <c r="C82" s="5" t="inlineStr">
+        <is>
+          <t>flood risk engineer Manchester</t>
+        </is>
+      </c>
+      <c r="D82" s="5" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E82" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F82" s="5" t="inlineStr">
+        <is>
+          <t>chip "flood risk engineer Manchester"</t>
+        </is>
+      </c>
+      <c r="G82" s="5" t="inlineStr"/>
+      <c r="H82" s="5" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>R082</t>
+        </is>
+      </c>
+      <c r="B83" s="5" t="inlineStr">
+        <is>
+          <t>UK: matching examples</t>
+        </is>
+      </c>
+      <c r="C83" s="5" t="inlineStr">
+        <is>
+          <t>renewable energy Scotland</t>
+        </is>
+      </c>
+      <c r="D83" s="5" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E83" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F83" s="5" t="inlineStr">
+        <is>
+          <t>chip "renewable energy Scotland"</t>
+        </is>
+      </c>
+      <c r="G83" s="5" t="inlineStr"/>
+      <c r="H83" s="5" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>R083</t>
+        </is>
+      </c>
+      <c r="B84" s="5" t="inlineStr">
+        <is>
+          <t>UK: contact</t>
+        </is>
+      </c>
+      <c r="C84" s="5" t="inlineStr">
+        <is>
+          <t>Correct the UK contact information — footer says “Calling From Ireland” / “Calling From Outside Ireland”</t>
+        </is>
+      </c>
+      <c r="D84" s="5" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E84" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F84" s="5" t="inlineStr">
+        <is>
+          <t>"Calling From Outside" only in for-keith quote</t>
+        </is>
+      </c>
+      <c r="G84" s="5" t="inlineStr"/>
+      <c r="H84" s="5" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t>R084</t>
+        </is>
+      </c>
+      <c r="B85" s="5" t="inlineStr">
+        <is>
+          <t>UK: contact</t>
+        </is>
+      </c>
+      <c r="C85" s="5" t="inlineStr">
+        <is>
+          <t>Calling from the UK: +44 28 4303 2055</t>
+        </is>
+      </c>
+      <c r="D85" s="5" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E85" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F85" s="5" t="inlineStr">
+        <is>
+          <t>/uk/ footer first line "Calling from the UK: +44 28 4303 2055"</t>
+        </is>
+      </c>
+      <c r="G85" s="5" t="inlineStr"/>
+      <c r="H85" s="5" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <t>R085</t>
+        </is>
+      </c>
+      <c r="B86" s="5" t="inlineStr">
+        <is>
+          <t>UK: contact</t>
+        </is>
+      </c>
+      <c r="C86" s="5" t="inlineStr">
+        <is>
+          <t>Calling from Ireland: (01) 912 5247</t>
+        </is>
+      </c>
+      <c r="D86" s="5" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E86" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F86" s="5" t="inlineStr">
+        <is>
+          <t>/uk/ footer second line "Calling from Ireland: (01) 912 5247"; IE footer lists Ireland first</t>
+        </is>
+      </c>
+      <c r="G86" s="5" t="inlineStr"/>
+      <c r="H86" s="5" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="8" t="inlineStr">
+        <is>
+          <t>R086</t>
+        </is>
+      </c>
+      <c r="B87" s="8" t="inlineStr">
+        <is>
+          <t>UK: contact</t>
+        </is>
+      </c>
+      <c r="C87" s="8" t="inlineStr">
+        <is>
+          <t>A GB number could also help. A Northern Ireland number may make some English employers assume the business primarily covers Ireland.</t>
+        </is>
+      </c>
+      <c r="D87" s="8" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E87" s="8" t="inlineStr">
+        <is>
+          <t>NEEDS CLIENT INPUT</t>
+        </is>
+      </c>
+      <c r="F87" s="8" t="inlineStr">
+        <is>
+          <t>Only +44 28 (NI) number on /uk/</t>
+        </is>
+      </c>
+      <c r="G87" s="8" t="inlineStr">
+        <is>
+          <t>Client must provide a GB number</t>
+        </is>
+      </c>
+      <c r="H87" s="8" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="5" t="inlineStr">
+        <is>
+          <t>R087</t>
+        </is>
+      </c>
+      <c r="B88" s="5" t="inlineStr">
+        <is>
+          <t>UK: sector classification</t>
+        </is>
+      </c>
+      <c r="C88" s="5" t="inlineStr">
+        <is>
+          <t>Highways Civil Engineer appears under “Built environment &amp; energy efficiency.” Should be under infrastructure, transportation or civil engineering.</t>
+        </is>
+      </c>
+      <c r="D88" s="5" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E88" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F88" s="5" t="inlineStr">
+        <is>
+          <t>/uk/jobs/11501402/ Sector row = "Sustainable infrastructure &amp; transport" only; jobs.json sectors ["Sustainable infrastructure &amp; transport"]</t>
+        </is>
+      </c>
+      <c r="G88" s="5" t="inlineStr">
+        <is>
+          <t>Built-environment tag dropped since v1</t>
+        </is>
+      </c>
+      <c r="H88" s="5" t="inlineStr">
+        <is>
+          <t>PARTIAL → DONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="5" t="inlineStr">
+        <is>
+          <t>R088</t>
+        </is>
+      </c>
+      <c r="B89" s="5" t="inlineStr">
+        <is>
+          <t>UK: sector classification</t>
+        </is>
+      </c>
+      <c r="C89" s="5" t="inlineStr">
+        <is>
+          <t>I would consider adding: Environmental engineering</t>
+        </is>
+      </c>
+      <c r="D89" s="5" t="inlineStr">
+        <is>
+          <t>IE+UK</t>
+        </is>
+      </c>
+      <c r="E89" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F89" s="5" t="inlineStr">
+        <is>
+          <t>IE "Environmental engineering" (8 roles); UK 0 roles so hidden ("No empty categories")</t>
+        </is>
+      </c>
+      <c r="G89" s="5" t="inlineStr"/>
+      <c r="H89" s="5" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="5" t="inlineStr">
+        <is>
+          <t>R089</t>
+        </is>
+      </c>
+      <c r="B90" s="5" t="inlineStr">
+        <is>
+          <t>UK: sector classification</t>
+        </is>
+      </c>
+      <c r="C90" s="5" t="inlineStr">
+        <is>
+          <t>Sustainable infrastructure</t>
+        </is>
+      </c>
+      <c r="D90" s="5" t="inlineStr">
+        <is>
+          <t>IE+UK</t>
+        </is>
+      </c>
+      <c r="E90" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F90" s="5" t="inlineStr">
+        <is>
+          <t>"Sustainable infrastructure &amp; transport" (IE 33 / UK 18)</t>
+        </is>
+      </c>
+      <c r="G90" s="5" t="inlineStr"/>
+      <c r="H90" s="5" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t>R090</t>
+        </is>
+      </c>
+      <c r="B91" s="6" t="inlineStr">
+        <is>
+          <t>UK: sector classification</t>
+        </is>
+      </c>
+      <c r="C91" s="6" t="inlineStr">
+        <is>
+          <t>Transport and active travel</t>
+        </is>
+      </c>
+      <c r="D91" s="6" t="inlineStr">
+        <is>
+          <t>IE+UK</t>
+        </is>
+      </c>
+      <c r="E91" s="6" t="inlineStr">
+        <is>
+          <t>INTERPRETED DIFFERENTLY</t>
+        </is>
+      </c>
+      <c r="F91" s="6" t="inlineStr">
+        <is>
+          <t>Merged into "Sustainable infrastructure &amp; transport"; no standalone transport/active-travel sector</t>
+        </is>
+      </c>
+      <c r="G91" s="6" t="inlineStr">
+        <is>
+          <t>Client to confirm the merge</t>
+        </is>
+      </c>
+      <c r="H91" s="6" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="5" t="inlineStr">
+        <is>
+          <t>R091</t>
+        </is>
+      </c>
+      <c r="B92" s="5" t="inlineStr">
+        <is>
+          <t>UK: sector classification</t>
+        </is>
+      </c>
+      <c r="C92" s="5" t="inlineStr">
+        <is>
+          <t>Climate and carbon</t>
+        </is>
+      </c>
+      <c r="D92" s="5" t="inlineStr">
+        <is>
+          <t>IE+UK</t>
+        </is>
+      </c>
+      <c r="E92" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F92" s="5" t="inlineStr">
+        <is>
+          <t>"Climate &amp; carbon" (IE 1 / UK 5)</t>
+        </is>
+      </c>
+      <c r="G92" s="5" t="inlineStr"/>
+      <c r="H92" s="5" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t>R092</t>
+        </is>
+      </c>
+      <c r="B93" s="5" t="inlineStr">
+        <is>
+          <t>UK: sector classification</t>
+        </is>
+      </c>
+      <c r="C93" s="5" t="inlineStr">
+        <is>
+          <t>Health, safety and environmental</t>
+        </is>
+      </c>
+      <c r="D93" s="5" t="inlineStr">
+        <is>
+          <t>IE+UK</t>
+        </is>
+      </c>
+      <c r="E93" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F93" s="5" t="inlineStr">
+        <is>
+          <t>"Health, safety &amp; environment" (IE 11 / UK 8)</t>
+        </is>
+      </c>
+      <c r="G93" s="5" t="inlineStr"/>
+      <c r="H93" s="5" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="5" t="inlineStr">
+        <is>
+          <t>R093</t>
+        </is>
+      </c>
+      <c r="B94" s="5" t="inlineStr">
+        <is>
+          <t>UK: sector classification</t>
+        </is>
+      </c>
+      <c r="C94" s="5" t="inlineStr">
+        <is>
+          <t>Nature recovery and biodiversity</t>
+        </is>
+      </c>
+      <c r="D94" s="5" t="inlineStr">
+        <is>
+          <t>IE+UK</t>
+        </is>
+      </c>
+      <c r="E94" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F94" s="5" t="inlineStr">
+        <is>
+          <t>"Ecology, nature recovery &amp; biodiversity" (IE 10 / UK 17)</t>
+        </is>
+      </c>
+      <c r="G94" s="5" t="inlineStr"/>
+      <c r="H94" s="5" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="5" t="inlineStr">
+        <is>
+          <t>R094</t>
+        </is>
+      </c>
+      <c r="B95" s="5" t="inlineStr">
+        <is>
+          <t>UK: sector classification</t>
+        </is>
+      </c>
+      <c r="C95" s="5" t="inlineStr">
+        <is>
+          <t>The categorisation must be consistent because the salary explorer and sector statistics depend on it.</t>
+        </is>
+      </c>
+      <c r="D95" s="5" t="inlineStr">
+        <is>
+          <t>IE+UK</t>
+        </is>
+      </c>
+      <c r="E95" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F95" s="5" t="inlineStr">
+        <is>
+          <t>Same 14-name taxonomy on jobs filter, sectors page, salary explorer, salary guide, dashboard and alert form (text dumps)</t>
+        </is>
+      </c>
+      <c r="G95" s="5" t="inlineStr"/>
+      <c r="H95" s="5" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="8" t="inlineStr">
+        <is>
+          <t>R095</t>
+        </is>
+      </c>
+      <c r="B96" s="8" t="inlineStr">
+        <is>
+          <t>UK: credibility signals</t>
+        </is>
+      </c>
+      <c r="C96" s="8" t="inlineStr">
+        <is>
+          <t>UK employer testimonials</t>
+        </is>
+      </c>
+      <c r="D96" s="8" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E96" s="8" t="inlineStr">
+        <is>
+          <t>NEEDS CLIENT INPUT</t>
+        </is>
+      </c>
+      <c r="F96" s="8" t="inlineStr">
+        <is>
+          <t>/uk/employers/ "Trusted across the UK — Client testimonials are being collected for launch."</t>
+        </is>
+      </c>
+      <c r="G96" s="8" t="inlineStr">
+        <is>
+          <t>Client must supply quotes</t>
+        </is>
+      </c>
+      <c r="H96" s="8" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="5" t="inlineStr">
+        <is>
+          <t>R096</t>
+        </is>
+      </c>
+      <c r="B97" s="5" t="inlineStr">
+        <is>
+          <t>UK: credibility signals</t>
+        </is>
+      </c>
+      <c r="C97" s="5" t="inlineStr">
+        <is>
+          <t>Recognisable organisations that have recruited through the network</t>
+        </is>
+      </c>
+      <c r="D97" s="5" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E97" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F97" s="5" t="inlineStr">
+        <is>
+          <t>/uk/employers/ + /uk/ marquee: Arup, Commonland, Dacorum BC, Environmental Standards Scotland, Gaia Talent, Grundon, Haskoning, Jacobs, … (12 logos)</t>
+        </is>
+      </c>
+      <c r="G97" s="5" t="inlineStr"/>
+      <c r="H97" s="5" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="8" t="inlineStr">
+        <is>
+          <t>R097</t>
+        </is>
+      </c>
+      <c r="B98" s="8" t="inlineStr">
+        <is>
+          <t>UK: credibility signals</t>
+        </is>
+      </c>
+      <c r="C98" s="8" t="inlineStr">
+        <is>
+          <t>Candidate and email audience figures</t>
+        </is>
+      </c>
+      <c r="D98" s="8" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E98" s="8" t="inlineStr">
+        <is>
+          <t>NEEDS CLIENT INPUT</t>
+        </is>
+      </c>
+      <c r="F98" s="8" t="inlineStr">
+        <is>
+          <t>"Monthly visitor figures are published at launch." / "Subscriber numbers are published at launch."</t>
+        </is>
+      </c>
+      <c r="G98" s="8" t="inlineStr"/>
+      <c r="H98" s="8" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="8" t="inlineStr">
+        <is>
+          <t>R098</t>
+        </is>
+      </c>
+      <c r="B99" s="8" t="inlineStr">
+        <is>
+          <t>UK: credibility signals</t>
+        </is>
+      </c>
+      <c r="C99" s="8" t="inlineStr">
+        <is>
+          <t>LinkedIn distribution</t>
+        </is>
+      </c>
+      <c r="D99" s="8" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E99" s="8" t="inlineStr">
+        <is>
+          <t>NEEDS CLIENT INPUT</t>
+        </is>
+      </c>
+      <c r="F99" s="8" t="inlineStr">
+        <is>
+          <t>"Network and follower numbers are published at launch."</t>
+        </is>
+      </c>
+      <c r="G99" s="8" t="inlineStr"/>
+      <c r="H99" s="8" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="9" t="inlineStr">
+        <is>
+          <t>R099</t>
+        </is>
+      </c>
+      <c r="B100" s="9" t="inlineStr">
+        <is>
+          <t>UK: credibility signals</t>
+        </is>
+      </c>
+      <c r="C100" s="9" t="inlineStr">
+        <is>
+          <t>Examples of UK placements or campaigns</t>
+        </is>
+      </c>
+      <c r="D100" s="9" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E100" s="9" t="inlineStr">
+        <is>
+          <t>NOT DONE</t>
+        </is>
+      </c>
+      <c r="F100" s="9" t="inlineStr">
+        <is>
+          <t>No placement or campaign example on /uk/employers/ or /uk/ (grep "placement", "campaign": 0)</t>
+        </is>
+      </c>
+      <c r="G100" s="9" t="inlineStr">
+        <is>
+          <t>Unchanged; needs client case material</t>
+        </is>
+      </c>
+      <c r="H100" s="9" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="5" t="inlineStr">
+        <is>
+          <t>R100</t>
+        </is>
+      </c>
+      <c r="B101" s="5" t="inlineStr">
+        <is>
+          <t>UK: credibility signals</t>
+        </is>
+      </c>
+      <c r="C101" s="5" t="inlineStr">
+        <is>
+          <t>Coverage across the ten-site specialist network</t>
+        </is>
+      </c>
+      <c r="D101" s="5" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E101" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F101" s="5" t="inlineStr">
+        <is>
+          <t>/uk/employers/ "Network coverage: conservationjobsuk.com … windjobsuk.com" (10) and "The network" chips on home</t>
+        </is>
+      </c>
+      <c r="G101" s="5" t="inlineStr"/>
+      <c r="H101" s="5" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="5" t="inlineStr">
+        <is>
+          <t>R101</t>
+        </is>
+      </c>
+      <c r="B102" s="5" t="inlineStr">
+        <is>
+          <t>UK: credibility signals</t>
+        </is>
+      </c>
+      <c r="C102" s="5" t="inlineStr">
+        <is>
+          <t>A clear UK advertising price or rate-card CTA</t>
+        </is>
+      </c>
+      <c r="D102" s="5" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E102" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F102" s="5" t="inlineStr">
+        <is>
+          <t>"Request advertising rates →" ×3 on /uk/employers/</t>
+        </is>
+      </c>
+      <c r="G102" s="5" t="inlineStr"/>
+      <c r="H102" s="5" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="5" t="inlineStr">
+        <is>
+          <t>R102</t>
+        </is>
+      </c>
+      <c r="B103" s="5" t="inlineStr">
+        <is>
+          <t>UK: credibility signals</t>
+        </is>
+      </c>
+      <c r="C103" s="5" t="inlineStr">
+        <is>
+          <t>The statement “19 employers hiring now” is worth retaining on the UK site.</t>
+        </is>
+      </c>
+      <c r="D103" s="5" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E103" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F103" s="5" t="inlineStr">
+        <is>
+          <t>/uk/ hero strip "18 employers hiring now" (live count)</t>
+        </is>
+      </c>
+      <c r="G103" s="5" t="inlineStr"/>
+      <c r="H103" s="5" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="5" t="inlineStr">
+        <is>
+          <t>R103</t>
+        </is>
+      </c>
+      <c r="B104" s="5" t="inlineStr">
+        <is>
+          <t>UK: proposition</t>
+        </is>
+      </c>
+      <c r="C104" s="5" t="inlineStr">
+        <is>
+          <t>Add a plain-English subheading beneath the tagline: Search environmental, ecology, sustainability, renewable-energy and low-carbon careers across the UK.</t>
+        </is>
+      </c>
+      <c r="D104" s="5" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E104" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F104" s="5" t="inlineStr">
+        <is>
+          <t>/uk/ hero subheading is the exact sentence</t>
+        </is>
+      </c>
+      <c r="G104" s="5" t="inlineStr"/>
+      <c r="H104" s="5" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="5" t="inlineStr">
+        <is>
+          <t>R104</t>
+        </is>
+      </c>
+      <c r="B105" s="5" t="inlineStr">
+        <is>
+          <t>UK: homepage order</t>
+        </is>
+      </c>
+      <c r="C105" s="5" t="inlineStr">
+        <is>
+          <t>Reduce homepage repetition — Regions, sectors and salary information each appear more than once.</t>
+        </is>
+      </c>
+      <c r="D105" s="5" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E105" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F105" s="5" t="inlineStr">
+        <is>
+          <t>/uk/: one region section, one sector section, one salary section</t>
+        </is>
+      </c>
+      <c r="G105" s="5" t="inlineStr"/>
+      <c r="H105" s="5" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="5" t="inlineStr">
+        <is>
+          <t>R105</t>
+        </is>
+      </c>
+      <c r="B106" s="5" t="inlineStr">
+        <is>
+          <t>UK: homepage order</t>
+        </is>
+      </c>
+      <c r="C106" s="5" t="inlineStr">
+        <is>
+          <t>Search and headline</t>
+        </is>
+      </c>
+      <c r="D106" s="5" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E106" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F106" s="5" t="inlineStr">
+        <is>
+          <t>/uk/ hero with search first</t>
+        </is>
+      </c>
+      <c r="G106" s="5" t="inlineStr"/>
+      <c r="H106" s="5" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="5" t="inlineStr">
+        <is>
+          <t>R106</t>
+        </is>
+      </c>
+      <c r="B107" s="5" t="inlineStr">
+        <is>
+          <t>UK: homepage order</t>
+        </is>
+      </c>
+      <c r="C107" s="5" t="inlineStr">
+        <is>
+          <t>Latest UK roles</t>
+        </is>
+      </c>
+      <c r="D107" s="5" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E107" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F107" s="5" t="inlineStr">
+        <is>
+          <t>"Latest UK roles" second</t>
+        </is>
+      </c>
+      <c r="G107" s="5" t="inlineStr"/>
+      <c r="H107" s="5" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="5" t="inlineStr">
+        <is>
+          <t>R107</t>
+        </is>
+      </c>
+      <c r="B108" s="5" t="inlineStr">
+        <is>
+          <t>UK: homepage order</t>
+        </is>
+      </c>
+      <c r="C108" s="5" t="inlineStr">
+        <is>
+          <t>Browse by sector</t>
+        </is>
+      </c>
+      <c r="D108" s="5" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E108" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F108" s="5" t="inlineStr">
+        <is>
+          <t>"Browse by sector" third</t>
+        </is>
+      </c>
+      <c r="G108" s="5" t="inlineStr"/>
+      <c r="H108" s="5" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="5" t="inlineStr">
+        <is>
+          <t>R108</t>
+        </is>
+      </c>
+      <c r="B109" s="5" t="inlineStr">
+        <is>
+          <t>UK: homepage order</t>
+        </is>
+      </c>
+      <c r="C109" s="5" t="inlineStr">
+        <is>
+          <t>Browse by region</t>
+        </is>
+      </c>
+      <c r="D109" s="5" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E109" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F109" s="5" t="inlineStr">
+        <is>
+          <t>"See where green employers are hiring" (region map) fourth</t>
+        </is>
+      </c>
+      <c r="G109" s="5" t="inlineStr"/>
+      <c r="H109" s="5" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="5" t="inlineStr">
+        <is>
+          <t>R109</t>
+        </is>
+      </c>
+      <c r="B110" s="5" t="inlineStr">
+        <is>
+          <t>UK: homepage order</t>
+        </is>
+      </c>
+      <c r="C110" s="5" t="inlineStr">
+        <is>
+          <t>Salary insights</t>
+        </is>
+      </c>
+      <c r="D110" s="5" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E110" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F110" s="5" t="inlineStr">
+        <is>
+          <t>"Salary insight" fifth</t>
+        </is>
+      </c>
+      <c r="G110" s="5" t="inlineStr"/>
+      <c r="H110" s="5" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="5" t="inlineStr">
+        <is>
+          <t>R110</t>
+        </is>
+      </c>
+      <c r="B111" s="5" t="inlineStr">
+        <is>
+          <t>UK: homepage order</t>
+        </is>
+      </c>
+      <c r="C111" s="5" t="inlineStr">
+        <is>
+          <t>Why GreenJobs</t>
+        </is>
+      </c>
+      <c r="D111" s="5" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E111" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F111" s="5" t="inlineStr">
+        <is>
+          <t>"Why GreenJobs" sixth</t>
+        </is>
+      </c>
+      <c r="G111" s="5" t="inlineStr"/>
+      <c r="H111" s="5" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="5" t="inlineStr">
+        <is>
+          <t>R111</t>
+        </is>
+      </c>
+      <c r="B112" s="5" t="inlineStr">
+        <is>
+          <t>UK: homepage order</t>
+        </is>
+      </c>
+      <c r="C112" s="5" t="inlineStr">
+        <is>
+          <t>Employers and advertising</t>
+        </is>
+      </c>
+      <c r="D112" s="5" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E112" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F112" s="5" t="inlineStr">
+        <is>
+          <t>"Employers and advertising" seventh</t>
+        </is>
+      </c>
+      <c r="G112" s="5" t="inlineStr"/>
+      <c r="H112" s="5" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="5" t="inlineStr">
+        <is>
+          <t>R112</t>
+        </is>
+      </c>
+      <c r="B113" s="5" t="inlineStr">
+        <is>
+          <t>UK: homepage order</t>
+        </is>
+      </c>
+      <c r="C113" s="5" t="inlineStr">
+        <is>
+          <t>Job alerts</t>
+        </is>
+      </c>
+      <c r="D113" s="5" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E113" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F113" s="5" t="inlineStr">
+        <is>
+          <t>"Job alerts: the week's green roles, in your inbox" last</t>
+        </is>
+      </c>
+      <c r="G113" s="5" t="inlineStr"/>
+      <c r="H113" s="5" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="5" t="inlineStr">
+        <is>
+          <t>R113</t>
+        </is>
+      </c>
+      <c r="B114" s="5" t="inlineStr">
+        <is>
+          <t>UK: homepage order</t>
+        </is>
+      </c>
+      <c r="C114" s="5" t="inlineStr">
+        <is>
+          <t>The animated “Map, Pay, Sectors” sequence could be reduced to one compact insights section.</t>
+        </is>
+      </c>
+      <c r="D114" s="5" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="E114" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F114" s="5" t="inlineStr">
+        <is>
+          <t>No animated Map/Pay/Sectors sequence; static region map + salary tiles</t>
+        </is>
+      </c>
+      <c r="G114" s="5" t="inlineStr"/>
+      <c r="H114" s="5" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="5" t="inlineStr">
+        <is>
+          <t>R114</t>
+        </is>
+      </c>
+      <c r="B115" s="5" t="inlineStr">
+        <is>
+          <t>UK: network positioning</t>
+        </is>
+      </c>
+      <c r="C115" s="5" t="inlineStr">
+        <is>
+          <t>Make the network much more prominent: Advertise once. Reach candidates across the GreenJobs specialist network. Your vacancy is automatically distributed to the most relevant environmental, ecology, renewable-energy, water, waste, wind and solar job sites.</t>
+        </is>
+      </c>
+      <c r="D115" s="5" t="inlineStr">
+        <is>
+          <t>IE+UK</t>
+        </is>
+      </c>
+      <c r="E115" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F115" s="5" t="inlineStr">
+        <is>
+          <t>Exact text as h1 + lede on /uk/employers/ and /ie/employers/, and as the home employer section lede</t>
+        </is>
+      </c>
+      <c r="G115" s="5" t="inlineStr"/>
+      <c r="H115" s="5" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H115"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -837,7 +5002,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2470,7 +6635,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3819,7 +7984,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4270,7 +8435,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/deliverables/greenjobs_redesign_2026-09-22/tests_register_2026-09-28.xlsx
+++ b/deliverables/greenjobs_redesign_2026-09-22/tests_register_2026-09-28.xlsx
@@ -10,18 +10,20 @@
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Keith requirements" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Coverage" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Manual cases" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Automated Python" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Automated Node" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Not automatable" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Layout regression" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Manual cases" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Not automatable" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Automated Python" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Automated Node" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Keith requirements'!$A$1:$H$115</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Coverage'!$A$1:$D$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Manual cases'!$A$1:$G$46</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Automated Python'!$A$1:$E$69</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Automated Node'!$A$1:$B$36</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Not automatable'!$A$1:$C$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Layout regression'!$A$1:$C$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Manual cases'!$A$1:$G$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Not automatable'!$A$1:$C$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Automated Python'!$A$1:$E$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Automated Node'!$A$1:$B$41</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -490,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -531,7 +533,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>68 test functions across 3 files; 575 checks (test_build run incl. companions) + 126 gap checks + 87 scraper checks; 0 failed, 0 skipped</t>
+          <t>84 test functions; 1,010 checks; 0 failed, 0 skipped</t>
         </is>
       </c>
     </row>
@@ -543,7 +545,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>35 node tests pass; plus 15 Playwright checks on the live dashboard DOM</t>
+          <t>40 node tests + 15 dashboard DOM checks + 1,732 layout-regression assertions (202 page loads, 3 viewports × 2 themes)</t>
         </is>
       </c>
     </row>
@@ -579,7 +581,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Coverage · Manual cases · Automated Python · Automated Node · Not automatable</t>
+          <t>Coverage · Keith requirements · Layout regression · Manual cases · Automated Python · Automated Node · Not automatable</t>
         </is>
       </c>
     </row>
@@ -616,6 +618,30 @@
       <c r="B12" t="inlineStr">
         <is>
           <t>All fixable ones fixed and re-screenshotted; see research/qa_2026-09-28/visual_issues_v2.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Full gate (run_all.py), final</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2,797 checks across 4 tiers, all green; layout suite 1,732/1,732</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Audit trail</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>research/qa_2026-09-28/: requirements matrix v1+v2, visual sweeps v1+v2, acceptance walk v3, panel re-run findings, pipeline audit v2</t>
         </is>
       </c>
     </row>
@@ -5008,6 +5034,247 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="90" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Rule</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Assertion</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>No horizontal overflow</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>document.scrollWidth ≤ viewport</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Chip anatomy</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>≤2 lines, dot on first text line, width ≥ dot+4px</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>R3</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Chip rows aligned</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>chips in one flex line share a top band ±4px</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Package table</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>cells inside column bands, row heights ±2px, no pills, fully visible ≥701px</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>No overlapping text</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>bounding boxes of text elements in a section don't intersect</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>R6</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>No clipped controls</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>buttons/links/inputs inside their scroll container; placeholder fits</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>R7</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Button rows</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>buttons in one row share height ±2px</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>R8</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Hero trust block</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>≤2 lines ≥1024px, ≤3 at 390px</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Filter rail</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>last control reachable at every viewport</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>R10</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Console</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>zero errors, zero failed requests</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>R11</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Contrast</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>≥4.5:1 body, ≥3:1 large text on solid backgrounds</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>R12</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Screenshot diff</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>≤1.5% pixels vs committed baseline (40 images)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:C13"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -6635,1807 +6902,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E69"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>Test function</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Purpose</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>check() calls</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Line</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>test_esc_and_json</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>test_build.py</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr"/>
-      <c r="D2" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="E2" s="4" t="n">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>test_parse_date</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>test_build.py</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr"/>
-      <c r="D3" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="E3" s="4" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>test_sectors</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>test_build.py</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr"/>
-      <c r="D4" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>test_regions</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>test_build.py</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr"/>
-      <c r="D5" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>test_sanitise_html</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>test_build.py</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr"/>
-      <c r="D6" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>test_salary_label</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>test_build.py</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr"/>
-      <c r="D7" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>test_image_size</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>test_build.py</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr"/>
-      <c r="D8" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>test_publish_text</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>test_build.py</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr"/>
-      <c r="D9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>test_guard_output</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>test_build.py</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr"/>
-      <c r="D10" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>test_check_dataset_rejects_bad_ids</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>test_build.py</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr"/>
-      <c r="D11" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>test_bad_id_fails_build</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>test_build.py</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr"/>
-      <c r="D12" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>test_plural_and_snapshot</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>test_build.py</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr"/>
-      <c r="D13" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="E13" s="4" t="n">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>test_employers_strip_is_honest</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>test_build.py</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr"/>
-      <c r="D14" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>test_render_fails_loudly</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>test_build.py</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr"/>
-      <c r="D15" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E15" s="4" t="n">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>test_fixture_build</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>test_build.py</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr"/>
-      <c r="D16" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="E16" s="4" t="n">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>test_real_data_build</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>test_build.py</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr"/>
-      <c r="D17" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="E17" s="4" t="n">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>test_validator_catches_injected_faults</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>test_build.py</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr"/>
-      <c r="D18" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="E18" s="4" t="n">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>test_dashboard_renders_per_edition</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>test_build.py</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr"/>
-      <c r="D19" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="E19" s="4" t="n">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>test_dashboard_kpis_edge_cases</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>test_build.py</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr"/>
-      <c r="D20" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E20" s="4" t="n">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>test_keith_pages_and_copy</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>test_build.py</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr"/>
-      <c r="D21" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="E21" s="4" t="n">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>test_taxonomy_infrastructure_roles</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>test_build.py</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr"/>
-      <c r="D22" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="E22" s="4" t="n">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>test_loc_class</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>test_build.py</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr"/>
-      <c r="D23" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="E23" s="4" t="n">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>test_agency_workplace_level_contract</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>test_build.py</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr"/>
-      <c r="D24" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="E24" s="4" t="n">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>test_currency_label_never_converts</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>test_build.py</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr"/>
-      <c r="D25" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="E25" s="4" t="n">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>test_similar_jobs_and_landings</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>test_build.py</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr"/>
-      <c r="D26" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="E26" s="4" t="n">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>test_hreflang_and_jsonld</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>test_build.py</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr"/>
-      <c r="D27" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="E27" s="4" t="n">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>test_ni_region_and_facets</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>test_build.py</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr"/>
-      <c r="D28" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="E28" s="4" t="n">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>test_pf_a_agency_rule</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>test_build.py</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr"/>
-      <c r="D29" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="E29" s="4" t="n">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>test_pf_a_loc_class_probes</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>test_build.py</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr"/>
-      <c r="D30" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="E30" s="4" t="n">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>test_pf_a_workplace_contract_level</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>test_build.py</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr"/>
-      <c r="D31" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="E31" s="4" t="n">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>test_pf_a_sector_golden_set</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>test_build.py</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr"/>
-      <c r="D32" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="E32" s="4" t="n">
-        <v>571</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>test_pf_a_dates_and_closed_roles</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>test_build.py</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr"/>
-      <c r="D33" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="E33" s="4" t="n">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>test_pf_a_currency_and_rounding</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>test_build.py</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr"/>
-      <c r="D34" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="E34" s="4" t="n">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>test_pf_a_garbled_pounds</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>test_build.py</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr"/>
-      <c r="D35" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E35" s="4" t="n">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>test_pf_a_landing_links</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>test_build.py</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="inlineStr"/>
-      <c r="D36" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="E36" s="4" t="n">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="4" t="inlineStr">
-        <is>
-          <t>test_pf_a_similar_jobs_rules</t>
-        </is>
-      </c>
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>test_build.py</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="inlineStr"/>
-      <c r="D37" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E37" s="4" t="n">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>test_pf_a_employer_count_phrase</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>test_build.py</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="inlineStr"/>
-      <c r="D38" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="E38" s="4" t="n">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>test_pf_a_hreflang_pairs</t>
-        </is>
-      </c>
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>test_build.py</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="inlineStr"/>
-      <c r="D39" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="E39" s="4" t="n">
-        <v>714</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>test_pf_a_validator_rules</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>test_build.py</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="inlineStr"/>
-      <c r="D40" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="E40" s="4" t="n">
-        <v>729</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="4" t="inlineStr">
-        <is>
-          <t>test_pf_a_scraper_floor</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>test_build.py</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="inlineStr"/>
-      <c r="D41" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="E41" s="4" t="n">
-        <v>769</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>test_pf_a_node_missing_fails_build</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>test_build.py</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="inlineStr"/>
-      <c r="D42" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E42" s="4" t="n">
-        <v>780</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t>test_panel_b_copy_and_consent</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t>test_build.py</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="inlineStr"/>
-      <c r="D43" s="4" t="n">
-        <v>33</v>
-      </c>
-      <c r="E43" s="4" t="n">
-        <v>862</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t>test_panel_b_dashboard_rules_from_stored_fields</t>
-        </is>
-      </c>
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t>test_build.py</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="inlineStr">
-        <is>
-          <t>dashboard_kpis must derive agency/remote from the stored fields and the median from annual_mid in the edition currency.</t>
-        </is>
-      </c>
-      <c r="D44" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="E44" s="4" t="n">
-        <v>953</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="4" t="inlineStr">
-        <is>
-          <t>test_parse_salary</t>
-        </is>
-      </c>
-      <c r="B45" s="4" t="inlineStr">
-        <is>
-          <t>test_scrape.py (recorded corpus)</t>
-        </is>
-      </c>
-      <c r="C45" s="4" t="inlineStr"/>
-      <c r="D45" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="E45" s="4" t="n">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="4" t="inlineStr">
-        <is>
-          <t>test_text_helpers</t>
-        </is>
-      </c>
-      <c r="B46" s="4" t="inlineStr">
-        <is>
-          <t>test_scrape.py (recorded corpus)</t>
-        </is>
-      </c>
-      <c r="C46" s="4" t="inlineStr"/>
-      <c r="D46" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="E46" s="4" t="n">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="4" t="inlineStr">
-        <is>
-          <t>test_parse_results_and_facets</t>
-        </is>
-      </c>
-      <c r="B47" s="4" t="inlineStr">
-        <is>
-          <t>test_scrape.py (recorded corpus)</t>
-        </is>
-      </c>
-      <c r="C47" s="4" t="inlineStr"/>
-      <c r="D47" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="E47" s="4" t="n">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="4" t="inlineStr">
-        <is>
-          <t>test_parse_job_fields</t>
-        </is>
-      </c>
-      <c r="B48" s="4" t="inlineStr">
-        <is>
-          <t>test_scrape.py (recorded corpus)</t>
-        </is>
-      </c>
-      <c r="C48" s="4" t="inlineStr"/>
-      <c r="D48" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="E48" s="4" t="n">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="4" t="inlineStr">
-        <is>
-          <t>test_measure_page</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>test_scrape.py (recorded corpus)</t>
-        </is>
-      </c>
-      <c r="C49" s="4" t="inlineStr"/>
-      <c r="D49" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E49" s="4" t="n">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="4" t="inlineStr">
-        <is>
-          <t>test_fetch_error_branches</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t>test_scrape.py (recorded corpus)</t>
-        </is>
-      </c>
-      <c r="C50" s="4" t="inlineStr"/>
-      <c r="D50" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="E50" s="4" t="n">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="4" t="inlineStr">
-        <is>
-          <t>test_snapshot_floor_and_atomic_write</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t>test_scrape.py (recorded corpus)</t>
-        </is>
-      </c>
-      <c r="C51" s="4" t="inlineStr"/>
-      <c r="D51" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="E51" s="4" t="n">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="4" t="inlineStr">
-        <is>
-          <t>test_crawl_ie</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="inlineStr">
-        <is>
-          <t>test_scrape.py (recorded corpus)</t>
-        </is>
-      </c>
-      <c r="C52" s="4" t="inlineStr"/>
-      <c r="D52" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="E52" s="4" t="n">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="4" t="inlineStr">
-        <is>
-          <t>test_crawl_uk_with_logos_and_paging</t>
-        </is>
-      </c>
-      <c r="B53" s="4" t="inlineStr">
-        <is>
-          <t>test_scrape.py (recorded corpus)</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="inlineStr"/>
-      <c r="D53" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="E53" s="4" t="n">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="4" t="inlineStr">
-        <is>
-          <t>test_crawl_paging_and_missing_page</t>
-        </is>
-      </c>
-      <c r="B54" s="4" t="inlineStr">
-        <is>
-          <t>test_scrape.py (recorded corpus)</t>
-        </is>
-      </c>
-      <c r="C54" s="4" t="inlineStr"/>
-      <c r="D54" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E54" s="4" t="n">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="4" t="inlineStr">
-        <is>
-          <t>test_snapshot_floor_rejects_and_main_exit_code</t>
-        </is>
-      </c>
-      <c r="B55" s="4" t="inlineStr">
-        <is>
-          <t>test_scrape.py (recorded corpus)</t>
-        </is>
-      </c>
-      <c r="C55" s="4" t="inlineStr"/>
-      <c r="D55" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E55" s="4" t="n">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="4" t="inlineStr">
-        <is>
-          <t>test_homepage_snapshot_fallback</t>
-        </is>
-      </c>
-      <c r="B56" s="4" t="inlineStr">
-        <is>
-          <t>test_scrape.py (recorded corpus)</t>
-        </is>
-      </c>
-      <c r="C56" s="4" t="inlineStr"/>
-      <c r="D56" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="E56" s="4" t="n">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="4" t="inlineStr">
-        <is>
-          <t>test_fixture_provenance</t>
-        </is>
-      </c>
-      <c r="B57" s="4" t="inlineStr">
-        <is>
-          <t>test_scrape.py (recorded corpus)</t>
-        </is>
-      </c>
-      <c r="C57" s="4" t="inlineStr"/>
-      <c r="D57" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E57" s="4" t="n">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="4" t="inlineStr">
-        <is>
-          <t>test_helper_edges</t>
-        </is>
-      </c>
-      <c r="B58" s="4" t="inlineStr">
-        <is>
-          <t>test_gaps.py (branch tests)</t>
-        </is>
-      </c>
-      <c r="C58" s="4" t="inlineStr"/>
-      <c r="D58" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="E58" s="4" t="n">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="4" t="inlineStr">
-        <is>
-          <t>test_dataset_and_brief</t>
-        </is>
-      </c>
-      <c r="B59" s="4" t="inlineStr">
-        <is>
-          <t>test_gaps.py (branch tests)</t>
-        </is>
-      </c>
-      <c r="C59" s="4" t="inlineStr"/>
-      <c r="D59" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="E59" s="4" t="n">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="4" t="inlineStr">
-        <is>
-          <t>test_hero_footage_variants</t>
-        </is>
-      </c>
-      <c r="B60" s="4" t="inlineStr">
-        <is>
-          <t>test_gaps.py (branch tests)</t>
-        </is>
-      </c>
-      <c r="C60" s="4" t="inlineStr"/>
-      <c r="D60" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="E60" s="4" t="n">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="4" t="inlineStr">
-        <is>
-          <t>test_geometry_helpers</t>
-        </is>
-      </c>
-      <c r="B61" s="4" t="inlineStr">
-        <is>
-          <t>test_gaps.py (branch tests)</t>
-        </is>
-      </c>
-      <c r="C61" s="4" t="inlineStr">
-        <is>
-          <t>svg_polygons / ring_area / point_in_rings / sample_map_points / film_payload</t>
-        </is>
-      </c>
-      <c r="D61" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="E61" s="4" t="n">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="4" t="inlineStr">
-        <is>
-          <t>test_escaping_in_rendered_html</t>
-        </is>
-      </c>
-      <c r="B62" s="4" t="inlineStr">
-        <is>
-          <t>test_gaps.py (branch tests)</t>
-        </is>
-      </c>
-      <c r="C62" s="4" t="inlineStr"/>
-      <c r="D62" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="E62" s="4" t="n">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="4" t="inlineStr">
-        <is>
-          <t>test_landing_zero_role_guard</t>
-        </is>
-      </c>
-      <c r="B63" s="4" t="inlineStr">
-        <is>
-          <t>test_gaps.py (branch tests)</t>
-        </is>
-      </c>
-      <c r="C63" s="4" t="inlineStr"/>
-      <c r="D63" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="E63" s="4" t="n">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="4" t="inlineStr">
-        <is>
-          <t>test_node_and_js_checks</t>
-        </is>
-      </c>
-      <c r="B64" s="4" t="inlineStr">
-        <is>
-          <t>test_gaps.py (branch tests)</t>
-        </is>
-      </c>
-      <c r="C64" s="4" t="inlineStr"/>
-      <c r="D64" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="E64" s="4" t="n">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="4" t="inlineStr">
-        <is>
-          <t>test_guard_output_edges</t>
-        </is>
-      </c>
-      <c r="B65" s="4" t="inlineStr">
-        <is>
-          <t>test_gaps.py (branch tests)</t>
-        </is>
-      </c>
-      <c r="C65" s="4" t="inlineStr"/>
-      <c r="D65" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E65" s="4" t="n">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="4" t="inlineStr">
-        <is>
-          <t>test_build_failure_exits</t>
-        </is>
-      </c>
-      <c r="B66" s="4" t="inlineStr">
-        <is>
-          <t>test_gaps.py (branch tests)</t>
-        </is>
-      </c>
-      <c r="C66" s="4" t="inlineStr"/>
-      <c r="D66" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="E66" s="4" t="n">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="4" t="inlineStr">
-        <is>
-          <t>test_rebuild_and_no_site_base</t>
-        </is>
-      </c>
-      <c r="B67" s="4" t="inlineStr">
-        <is>
-          <t>test_gaps.py (branch tests)</t>
-        </is>
-      </c>
-      <c r="C67" s="4" t="inlineStr"/>
-      <c r="D67" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="E67" s="4" t="n">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="4" t="inlineStr">
-        <is>
-          <t>test_cli_main_with_today</t>
-        </is>
-      </c>
-      <c r="B68" s="4" t="inlineStr">
-        <is>
-          <t>test_gaps.py (branch tests)</t>
-        </is>
-      </c>
-      <c r="C68" s="4" t="inlineStr"/>
-      <c r="D68" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E68" s="4" t="n">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="4" t="inlineStr">
-        <is>
-          <t>test_validator_every_message</t>
-        </is>
-      </c>
-      <c r="B69" s="4" t="inlineStr">
-        <is>
-          <t>test_gaps.py (branch tests)</t>
-        </is>
-      </c>
-      <c r="C69" s="4" t="inlineStr"/>
-      <c r="D69" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="E69" s="4" t="n">
-        <v>383</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:E69"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B36"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="90" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>Test name</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>lib.test.js</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>salaryLabel formats ranges, singles and rates</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>lib.test.js</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>annual annualises hourly and rejects junk</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>lib.test.js</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>filterJobs honours every state key and sorts</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>lib.test.js</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>URL state round-trips and drops defaults</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>lib.test.js</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>parseState skips malformed percent-escapes instead of throwing</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>lib.test.js</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>jobUrl joins dataset hrefs onto the page-relative jobs base</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>lib.test.js</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>histogram bins on the left edge, last band open</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>lib.test.js</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>median and money</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>lib.test.js</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>smart match ranks by term overlap and returns matched terms</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>lib.test.js</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>suggest finds roles, sectors and places</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>lib.test.js</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>compass scoring is deterministic and hash round-trips</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>lib.test.js</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>treemap fills the box exactly</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>lib.test.js</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>daysAgo / ago</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>lib.test.js</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>stem meets ecologist / ecology / ecological</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>lib.test.js</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>fitMatch ranks title + place matches first and reports terms</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>lib.test.js</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>salaryPosition reports range, disclosure share and percentiles</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>lib.test.js</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>encodeFit / decodeFit round-trip distinct terms</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>lib.test.js</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>filmScrub holds, travels and fills the rail</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>lib.test.js</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>easeOutQuart and countAt</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>lib.test.js</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>salaryLabel never converts the advertised currency; it adds an approximate equivalent</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>lib.test.js</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>annual compares in the edition currency but leaves the label alone</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>lib.test.js</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>locLabel maps every class</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>lib.test.js</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>filterJobs: workplace, level, contract, salary range, only-toggle, closing, agency</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>lib.test.js</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>URL state carries every facet and Clear resets it</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>lib.test.js</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>daysUntil / daysAgo use whole calendar days against the build date</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>lib.test.js</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>closingWithin (0..7) and newThisWeek (0..6) mirror build_site</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>lib.test.js</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>setToday pins the build date for every date helper</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>lib.test.js</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>filterJobs sector accepts "|"-joined any-of values (multi-sector landing links)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>lib.test.js</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>annual excludes USD and unknown currencies from comparisons; the label still shows them</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>lib.test.js</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>money rounds half up like Python rnd()</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>dashboard.test.js</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>csvCell quotes commas, quotes and newlines only when needed</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>dashboard.test.js</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>toCsv joins rows with CRLF and a trailing newline</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>dashboard.test.js</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>kpiRows flattens the payload with a header and every sector, region and score</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>dashboard.test.js</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>csvCell neutralises spreadsheet formula prefixes</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>dashboard.test.js</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>kpiRows labels the advertised window and describes the agency rule</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:B36"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8572,4 +7039,2200 @@
   <autoFilter ref="A1:C7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E85"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Test function</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Purpose</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>check() calls</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>test_esc_and_json</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>test_build.py</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr"/>
+      <c r="D2" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>test_parse_date</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>test_build.py</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr"/>
+      <c r="D3" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>test_sectors</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>test_build.py</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr"/>
+      <c r="D4" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>test_regions</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>test_build.py</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr"/>
+      <c r="D5" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>test_sanitise_html</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>test_build.py</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr"/>
+      <c r="D6" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>test_salary_label</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>test_build.py</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr"/>
+      <c r="D7" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>test_image_size</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>test_build.py</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr"/>
+      <c r="D8" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>test_publish_text</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>test_build.py</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr"/>
+      <c r="D9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>test_guard_output</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>test_build.py</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr"/>
+      <c r="D10" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>test_check_dataset_rejects_bad_ids</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>test_build.py</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr"/>
+      <c r="D11" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>test_bad_id_fails_build</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>test_build.py</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr"/>
+      <c r="D12" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>test_plural_and_snapshot</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>test_build.py</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr"/>
+      <c r="D13" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>test_employers_strip_is_honest</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>test_build.py</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr"/>
+      <c r="D14" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>test_render_fails_loudly</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>test_build.py</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr"/>
+      <c r="D15" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>test_fixture_build</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>test_build.py</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr"/>
+      <c r="D16" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>test_real_data_build</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>test_build.py</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr"/>
+      <c r="D17" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>test_validator_catches_injected_faults</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>test_build.py</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr"/>
+      <c r="D18" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>test_dashboard_renders_per_edition</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>test_build.py</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr"/>
+      <c r="D19" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>test_dashboard_kpis_edge_cases</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>test_build.py</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr"/>
+      <c r="D20" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>test_keith_pages_and_copy</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>test_build.py</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr"/>
+      <c r="D21" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>test_taxonomy_infrastructure_roles</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>test_build.py</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr"/>
+      <c r="D22" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>test_loc_class</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>test_build.py</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr"/>
+      <c r="D23" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>test_agency_workplace_level_contract</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>test_build.py</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr"/>
+      <c r="D24" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="E24" s="4" t="n">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>test_currency_label_never_converts</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>test_build.py</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr"/>
+      <c r="D25" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="E25" s="4" t="n">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>test_similar_jobs_and_landings</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>test_build.py</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr"/>
+      <c r="D26" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="E26" s="4" t="n">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>test_hreflang_and_jsonld</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>test_build.py</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr"/>
+      <c r="D27" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="E27" s="4" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>test_ni_region_and_facets</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>test_build.py</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr"/>
+      <c r="D28" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="E28" s="4" t="n">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>test_pf_a_agency_rule</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>test_build.py</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr"/>
+      <c r="D29" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E29" s="4" t="n">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>test_pf_a_loc_class_probes</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>test_build.py</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr"/>
+      <c r="D30" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="E30" s="4" t="n">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>test_pf_a_workplace_contract_level</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>test_build.py</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr"/>
+      <c r="D31" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="E31" s="4" t="n">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>test_pf_a_sector_golden_set</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>test_build.py</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr"/>
+      <c r="D32" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E32" s="4" t="n">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>test_pf_a_dates_and_closed_roles</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>test_build.py</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr"/>
+      <c r="D33" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="E33" s="4" t="n">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>test_pf_a_currency_and_rounding</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>test_build.py</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr"/>
+      <c r="D34" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E34" s="4" t="n">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>test_pf_a_garbled_pounds</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>test_build.py</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr"/>
+      <c r="D35" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E35" s="4" t="n">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>test_pf_a_landing_links</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>test_build.py</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr"/>
+      <c r="D36" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E36" s="4" t="n">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>test_pf_a_similar_jobs_rules</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>test_build.py</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr"/>
+      <c r="D37" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" s="4" t="n">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>test_pf_a_employer_count_phrase</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>test_build.py</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr"/>
+      <c r="D38" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E38" s="4" t="n">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>test_pf_a_hreflang_pairs</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>test_build.py</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr"/>
+      <c r="D39" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E39" s="4" t="n">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>test_pf_a_validator_rules</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>test_build.py</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr"/>
+      <c r="D40" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="E40" s="4" t="n">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>test_pf_a_scraper_floor</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>test_build.py</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr"/>
+      <c r="D41" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E41" s="4" t="n">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>test_pf_a_node_missing_fails_build</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>test_build.py</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr"/>
+      <c r="D42" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" s="4" t="n">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>test_r3_visual_fixes</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>test_build.py</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>Round-3 visual sweep (visual_issues_v2): N4 long dates, N5 no IE employer count,</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="E43" s="4" t="n">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>test_panel_b_copy_and_consent</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>test_build.py</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr"/>
+      <c r="D44" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="E44" s="4" t="n">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>test_panel_b_dashboard_rules_from_stored_fields</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>test_build.py</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>dashboard_kpis must derive agency/remote from the stored fields and the median from annual_mid in the edition currency.</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E45" s="4" t="n">
+        <v>1082</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>test_r2a_secondary_sector_tags</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>test_build.py</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr"/>
+      <c r="D46" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E46" s="4" t="n">
+        <v>1105</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>test_r2a_cross_border_phrases</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>test_build.py</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr"/>
+      <c r="D47" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E47" s="4" t="n">
+        <v>1134</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>test_r2a_facts_copy_and_facets</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>test_build.py</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr"/>
+      <c r="D48" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="E48" s="4" t="n">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>test_r2a_landing_intro_length</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>test_build.py</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr"/>
+      <c r="D49" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" s="4" t="n">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>test_r2a_regions_and_pairs</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>test_build.py</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr"/>
+      <c r="D50" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E50" s="4" t="n">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>test_r2a_real_build_checks</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>test_build.py</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr"/>
+      <c r="D51" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="E51" s="4" t="n">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>test_r2b_visitor_voice_and_shell</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>test_build.py</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr"/>
+      <c r="D52" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="E52" s="4" t="n">
+        <v>1262</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>test_r4_sterling_figure_fidelity</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>test_build.py</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>Item 1: a slug shared by three adverts must not hand an IE role the wrong sterling figure.</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E53" s="4" t="n">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>test_r4_secondary_sectors_and_enforcement</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>test_build.py</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>Item 2: title / site-label / energy-family secondaries survive the ratio rule; golden expected-present set.</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E54" s="4" t="n">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>test_r4_workplace_contract_cross_dates</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>test_build.py</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>Items 3-4: SITE_WORDS, contract type-wins, CROSS_RE separators and scope, date_long(None).</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="E55" s="4" t="n">
+        <v>1355</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>test_r4_unverified_excluded_from_figures</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>test_build.py</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>Item 5: roles flagged unverified_cur never enter medians, bands or the salary guide; the fx note says so.</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E56" s="4" t="n">
+        <v>1378</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>test_r4_real_build_marker_hero_notes</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>test_build.py</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>Items 5-8 on real data: OK marker, hero facts, fx note, dashboard voice, validator CLI.</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="E57" s="4" t="n">
+        <v>1392</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>test_r4_scraper_and_runner</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>test_build.py</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>Item 6: --site both fails when either site is rejected; logos.json atomic; run_all SKIP semantics.</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E58" s="4" t="n">
+        <v>1439</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>test_r4b_landings_strip_types</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>test_build.py</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>Coordinator follow-ups: landing loc filter, static strip under six employers, type casing, one guide date, wording.</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="E59" s="4" t="n">
+        <v>1461</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>test_round4_b_copy_css_js</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>test_build.py</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr"/>
+      <c r="D60" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="E60" s="4" t="n">
+        <v>1507</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>test_parse_salary</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>test_scrape.py</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr"/>
+      <c r="D61" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="E61" s="4" t="n">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>test_text_helpers</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>test_scrape.py</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr"/>
+      <c r="D62" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="E62" s="4" t="n">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>test_parse_results_and_facets</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>test_scrape.py</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr"/>
+      <c r="D63" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="E63" s="4" t="n">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>test_parse_job_fields</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>test_scrape.py</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr"/>
+      <c r="D64" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="E64" s="4" t="n">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>test_measure_page</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>test_scrape.py</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr"/>
+      <c r="D65" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E65" s="4" t="n">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>test_fetch_error_branches</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>test_scrape.py</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr"/>
+      <c r="D66" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E66" s="4" t="n">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>test_snapshot_floor_and_atomic_write</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>test_scrape.py</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr"/>
+      <c r="D67" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="E67" s="4" t="n">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>test_crawl_ie</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>test_scrape.py</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr"/>
+      <c r="D68" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="E68" s="4" t="n">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>test_crawl_uk_with_logos_and_paging</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>test_scrape.py</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr"/>
+      <c r="D69" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="E69" s="4" t="n">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>test_crawl_paging_and_missing_page</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>test_scrape.py</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr"/>
+      <c r="D70" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E70" s="4" t="n">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>test_snapshot_floor_rejects_and_main_exit_code</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>test_scrape.py</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr"/>
+      <c r="D71" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E71" s="4" t="n">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>test_homepage_snapshot_fallback</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>test_scrape.py</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr"/>
+      <c r="D72" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E72" s="4" t="n">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>test_fixture_provenance</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>test_scrape.py</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr"/>
+      <c r="D73" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E73" s="4" t="n">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>test_helper_edges</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>test_gaps.py</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr"/>
+      <c r="D74" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="E74" s="4" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>test_dataset_and_brief</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>test_gaps.py</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr"/>
+      <c r="D75" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="E75" s="4" t="n">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>test_hero_footage_variants</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t>test_gaps.py</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr"/>
+      <c r="D76" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="E76" s="4" t="n">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>test_geometry_helpers</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>test_gaps.py</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>svg_polygons / ring_area / point_in_rings / sample_map_points / film_payload</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E77" s="4" t="n">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t>test_escaping_in_rendered_html</t>
+        </is>
+      </c>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>test_gaps.py</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr"/>
+      <c r="D78" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="E78" s="4" t="n">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>test_landing_zero_role_guard</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>test_gaps.py</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr"/>
+      <c r="D79" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="E79" s="4" t="n">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>test_node_and_js_checks</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>test_gaps.py</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr"/>
+      <c r="D80" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="E80" s="4" t="n">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>test_guard_output_edges</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>test_gaps.py</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr"/>
+      <c r="D81" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E81" s="4" t="n">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>test_build_failure_exits</t>
+        </is>
+      </c>
+      <c r="B82" s="4" t="inlineStr">
+        <is>
+          <t>test_gaps.py</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr"/>
+      <c r="D82" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E82" s="4" t="n">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="4" t="inlineStr">
+        <is>
+          <t>test_rebuild_and_no_site_base</t>
+        </is>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>test_gaps.py</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr"/>
+      <c r="D83" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E83" s="4" t="n">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="4" t="inlineStr">
+        <is>
+          <t>test_cli_main_with_today</t>
+        </is>
+      </c>
+      <c r="B84" s="4" t="inlineStr">
+        <is>
+          <t>test_gaps.py</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="inlineStr"/>
+      <c r="D84" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E84" s="4" t="n">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="4" t="inlineStr">
+        <is>
+          <t>test_validator_every_message</t>
+        </is>
+      </c>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t>test_gaps.py</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="inlineStr"/>
+      <c r="D85" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E85" s="4" t="n">
+        <v>383</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E85"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="90" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Test name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>lib.test.js</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>salaryLabel formats ranges, singles and rates</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>lib.test.js</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>annual annualises hourly and rejects junk</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>lib.test.js</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>filterJobs honours every state key and sorts</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>lib.test.js</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>URL state round-trips and drops defaults</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>lib.test.js</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>parseState skips malformed percent-escapes instead of throwing</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>lib.test.js</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>jobUrl joins dataset hrefs onto the page-relative jobs base</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>lib.test.js</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>histogram bins on the left edge, last band open</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>lib.test.js</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>median and money</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>lib.test.js</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>smart match ranks by term overlap and returns matched terms</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>lib.test.js</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>suggest finds roles, sectors and places</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>lib.test.js</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>compass scoring is deterministic and hash round-trips</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>lib.test.js</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>treemap fills the box exactly</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>lib.test.js</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>daysAgo / ago</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>lib.test.js</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>stem meets ecologist / ecology / ecological</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>lib.test.js</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>fitMatch ranks title + place matches first and reports terms</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>lib.test.js</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>salaryPosition reports range, disclosure share and percentiles</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>lib.test.js</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>encodeFit / decodeFit round-trip distinct terms</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>lib.test.js</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>filmScrub holds, travels and fills the rail</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>lib.test.js</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>easeOutQuart and countAt</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>lib.test.js</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>salaryLabel never converts the advertised currency; it adds an approximate equivalent</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>lib.test.js</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>annual compares in the edition currency but leaves the label alone</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>lib.test.js</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>locLabel maps every class</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>lib.test.js</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>filterJobs: workplace, level, contract, salary range, only-toggle, closing, agency</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>lib.test.js</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>URL state carries every facet and Clear resets it</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>lib.test.js</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>daysUntil / daysAgo use whole calendar days against the build date</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>lib.test.js</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>closingWithin (0..7) and newThisWeek (0..6) mirror build_site</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>lib.test.js</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>setToday pins the build date for every date helper</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>lib.test.js</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>filterJobs sector accepts "|"-joined any-of values (multi-sector landing links)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>lib.test.js</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>annual excludes USD and unknown currencies from comparisons; the label still shows them</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>lib.test.js</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>money rounds half up like Python rnd()</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>lib.test.js</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>normaliseState folds the legacy type param into contract / workplace</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>lib.test.js</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>dedupeJobs keeps one entry per title + employer</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>lib.test.js</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>compass pct is 100 only when every answer favoured the sector</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>lib.test.js</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>orderSectors puts the active filter sector first</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>lib.test.js</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>suggestSectors respects the other active facets</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>dashboard.test.js</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>csvCell quotes commas, quotes and newlines only when needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>dashboard.test.js</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>toCsv joins rows with CRLF and a trailing newline</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>dashboard.test.js</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>kpiRows flattens the payload with a header and every sector, region and score</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>dashboard.test.js</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>csvCell neutralises spreadsheet formula prefixes</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>dashboard.test.js</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>kpiRows labels the advertised window and describes the agency rule</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:B41"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/deliverables/greenjobs_redesign_2026-09-22/tests_register_2026-09-28.xlsx
+++ b/deliverables/greenjobs_redesign_2026-09-22/tests_register_2026-09-28.xlsx
@@ -15,6 +15,7 @@
     <sheet name="Not automatable" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Automated Python" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Automated Node" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Human-eye rounds" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Keith requirements'!$A$1:$H$115</definedName>
@@ -492,7 +493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -513,6 +514,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
@@ -521,7 +523,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PASS — 165 roles, 195 pages, CSS 69.7/80 KB, JS 97.8/125 KB</t>
+          <t>PASS — 165 roles, 195 pages, CSS 79.3/80 KB, JS 111.3/125 KB (2026-09-30)</t>
         </is>
       </c>
     </row>
@@ -533,7 +535,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>84 test functions; 1,010 checks; 0 failed, 0 skipped</t>
+          <t>1,258 checks (build + validate + scrape + gaps); 0 failed, 0 skipped (2026-09-30)</t>
         </is>
       </c>
     </row>
@@ -545,7 +547,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>40 node tests + 15 dashboard DOM checks + 1,732 layout-regression assertions (202 page loads, 3 viewports × 2 themes)</t>
+          <t>42 node tests + 15 dashboard DOM checks + 1,732 layout-regression assertions (202 page loads, 3 viewports × 2 themes); run_all.py total 3,047</t>
         </is>
       </c>
     </row>
@@ -557,7 +559,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>45 cases listed; QA lens ran 34, 28 PASS, 2 FAIL (both fixed since), 4 PARTIAL</t>
+          <t>Functional walk (walk.js) 134/134 on both editions at 1440 and 390; 45 manual cases listed</t>
         </is>
       </c>
     </row>
@@ -642,6 +644,56 @@
       <c r="B14" t="inlineStr">
         <is>
           <t>research/qa_2026-09-28/: requirements matrix v1+v2, visual sweeps v1+v2, acceptance walk v3, panel re-run findings, pipeline audit v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Human-eye release gate (skill human-eye-test)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>4 rounds, 180-shot matrix read image by image; r1 37 → r2 20 → r3 13 → r4 8 defects; all P1/P2 fixed, 3 P3 accepted; verdict: research/qa_2026-09-28/human_eye_verdict.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Site-manager requests (2026-09-29)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Package table Premium posting + Membership only; full job-description preview — both editions, verified by walk.js B1–B4 and pipeline audit</t>
         </is>
       </c>
     </row>
@@ -7047,7 +7099,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E85"/>
+  <dimension ref="A1:E86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -8718,6 +8770,26 @@
       </c>
       <c r="E85" s="4" t="n">
         <v>383</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>test_publish_text</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>publish_text(css=True) joins after { } ; , only; quoted ; kept</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -8732,7 +8804,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B41"/>
+  <dimension ref="A1:B42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -9231,8 +9303,202 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>lib.test.js</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:B41"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="90" customWidth="1" min="6" max="6"/>
+    <col width="55" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Round</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Defects found</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Accepted</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Highlights</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Evidence file</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>r1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>37</v>
+      </c>
+      <c r="D2" t="n">
+        <v>37</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>mobile table Standard column, map chips, cross-page stats mismatch, closed/unverified job headers</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>research/qa_2026-09-28/human_eye/DEFECTS.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>r2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>20</v>
+      </c>
+      <c r="D3" t="n">
+        <v>20</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>separator pairs, dark carousel mask, Membership ticks, sterling source line, NI map label</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>research/qa_2026-09-28/human_eye/DEFECTS_r2.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>r3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>13</v>
+      </c>
+      <c r="D4" t="n">
+        <v>13</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>sticky thead at 1024, salary labels + €/£ prefix, dashboard tile copy, single Location row, treemap labels</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>research/qa_2026-09-28/human_eye/DEFECTS_r3.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>r4</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>8</v>
+      </c>
+      <c r="D5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>dashboard clamp removed, one salary band set on every device, UK/IE chip wording, subscribe copy; accepted: 1024 chart label size, cookie dialog focus, wrapped snapshot chip</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>research/qa_2026-09-28/human_eye_verdict.md</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>